--- a/Data_Table/밸런스 시뮬레이터.xlsx
+++ b/Data_Table/밸런스 시뮬레이터.xlsx
@@ -641,7 +641,6 @@
       <c r="C9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -657,7 +656,6 @@
       <c r="C10" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -793,7 +791,6 @@
       <c r="C17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -909,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="I23" t="n">
         <v>6</v>
@@ -941,10 +938,10 @@
         <v>12</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>65</v>
@@ -973,10 +970,10 @@
         <v>16</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>80</v>
@@ -1005,10 +1002,10 @@
         <v>20</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>560</v>
+        <v>720</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>96</v>
@@ -1037,10 +1034,10 @@
         <v>24</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>770</v>
+        <v>1700</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>102</v>
@@ -1069,10 +1066,10 @@
         <v>27</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2420</v>
+        <v>4070</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>141</v>
@@ -1101,10 +1098,10 @@
         <v>30</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>9920</v>
+        <v>17750</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>155</v>
@@ -1133,10 +1130,10 @@
         <v>33</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>42000</v>
+        <v>27000</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>180</v>
@@ -1165,10 +1162,10 @@
         <v>36</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>87000</v>
+        <v>45000</v>
       </c>
       <c r="I31" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>210</v>
@@ -1197,10 +1194,10 @@
         <v>39</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>328000</v>
+        <v>165000</v>
       </c>
       <c r="I32" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>250</v>
@@ -1229,10 +1226,10 @@
         <v>42</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>742000</v>
+        <v>378000</v>
       </c>
       <c r="I33" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>295</v>
@@ -1261,10 +1258,10 @@
         <v>45</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1872000</v>
+        <v>1076000</v>
       </c>
       <c r="I34" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>345</v>
@@ -1293,10 +1290,10 @@
         <v>48</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3299000</v>
+        <v>1613000</v>
       </c>
       <c r="I35" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>400</v>
@@ -1325,10 +1322,10 @@
         <v>51</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>4945000</v>
+        <v>2416000</v>
       </c>
       <c r="I36" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>460</v>
@@ -1357,10 +1354,10 @@
         <v>54</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>11154000</v>
+        <v>4032000</v>
       </c>
       <c r="I37" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>525</v>
@@ -1412,10 +1409,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.79</v>
+        <v>7.97</v>
       </c>
       <c r="C4" t="n">
-        <v>14.52</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1438,10 +1435,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1451,10 +1448,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.79</v>
+        <v>13.65</v>
       </c>
       <c r="C7" t="n">
-        <v>16.43</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="8">
@@ -1477,10 +1474,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1490,10 +1487,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.15</v>
+        <v>1.04</v>
       </c>
       <c r="C10" t="n">
-        <v>2.57</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.17</v>
+        <v>2.61</v>
       </c>
       <c r="C11" t="n">
-        <v>6.36</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="12">
@@ -1516,10 +1513,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.17</v>
+        <v>2.61</v>
       </c>
       <c r="C12" t="n">
-        <v>6.36</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="13">
@@ -1529,10 +1526,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.71</v>
+        <v>3.81</v>
       </c>
       <c r="C13" t="n">
-        <v>7.28</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="14">
@@ -1542,10 +1539,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.39</v>
+        <v>4.65</v>
       </c>
       <c r="C14" t="n">
-        <v>9.17</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="15">
@@ -1555,10 +1552,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.359999999999999</v>
+        <v>6.71</v>
       </c>
       <c r="C15" t="n">
-        <v>11.74</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="16">
@@ -1568,10 +1565,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.79</v>
+        <v>7.97</v>
       </c>
       <c r="C16" t="n">
-        <v>14.52</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1581,7 +1578,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -1594,10 +1591,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1620,10 +1617,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1633,10 +1630,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1646,10 +1643,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1659,7 +1656,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -1675,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1685,10 +1682,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1698,10 +1695,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1711,10 +1708,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1724,10 +1721,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1737,10 +1734,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2006,7 +2003,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2093,18 +2090,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="6" t="n">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="E5" t="n">
         <v>72</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>12.5</v>
+        <v>13.21</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -2180,18 +2177,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="6" t="n">
-        <v>781</v>
+        <v>873</v>
       </c>
       <c r="E6" t="n">
         <v>72</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>15.62</v>
+        <v>17.46</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -2276,16 +2273,16 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1410</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>108</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>28.12</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8">
         <f>IF($E7*'설정'!$C$5*IF(('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)&lt;1,('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)^(-'설정'!$C$6),('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E7*'설정'!$C$5*IF(('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)&lt;1,('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)^(-'설정'!$C$6),('설정'!$C$22*IF($A7&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D7)^(-'설정'!$C$7)),0))</f>
@@ -2358,21 +2355,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="6" t="n">
-        <v>1860</v>
+        <v>1360</v>
       </c>
       <c r="E8" t="n">
         <v>72</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>37.12</v>
+        <v>27.21</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="8">
         <f>IF($E8*'설정'!$C$5*IF(('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)&lt;1,('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)^(-'설정'!$C$6),('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E8*'설정'!$C$5*IF(('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)&lt;1,('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)^(-'설정'!$C$6),('설정'!$C$22*IF($A8&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D8)^(-'설정'!$C$7)),0))</f>
@@ -2450,16 +2447,16 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="6" t="n">
-        <v>2450</v>
+        <v>1600</v>
       </c>
       <c r="E9" t="n">
         <v>72</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>49.01</v>
+        <v>32.09</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="8">
         <f>IF($E9*'설정'!$C$5*IF(('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)&lt;1,('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)^(-'설정'!$C$6),('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E9*'설정'!$C$5*IF(('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)&lt;1,('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)^(-'설정'!$C$6),('설정'!$C$22*IF($A9&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D9)^(-'설정'!$C$7)),0))</f>
@@ -2537,16 +2534,16 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="6" t="n">
-        <v>3230</v>
+        <v>1890</v>
       </c>
       <c r="E10" t="n">
         <v>72</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>64.69</v>
+        <v>37.84</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="8">
         <f>IF($E10*'설정'!$C$5*IF(('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)&lt;1,('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)^(-'설정'!$C$6),('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E10*'설정'!$C$5*IF(('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)&lt;1,('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)^(-'설정'!$C$6),('설정'!$C$22*IF($A10&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D10)^(-'설정'!$C$7)),0))</f>
@@ -2619,21 +2616,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="6" t="n">
-        <v>4270</v>
+        <v>2900</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>85.39</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" s="8">
         <f>IF($E11*'설정'!$C$5*IF(('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)&lt;1,('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$6),('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E11*'설정'!$C$5*IF(('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)&lt;1,('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$6),('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$7)),0))</f>
@@ -2706,7 +2703,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2715,16 +2712,16 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>5640</v>
+        <v>3010</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>113</v>
+        <v>60.21</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H12" s="8">
         <f>IF($E12*'설정'!$C$5*IF(('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)&lt;1,('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$6),('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E12*'설정'!$C$5*IF(('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)&lt;1,('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$6),('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$7)),0))</f>
@@ -2802,16 +2799,16 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>7440</v>
+        <v>3070</v>
       </c>
       <c r="E13" t="n">
         <v>72</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>149</v>
+        <v>61.44</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H13" s="8">
         <f>IF($E13*'설정'!$C$5*IF(('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)&lt;1,('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$6),('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E13*'설정'!$C$5*IF(('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)&lt;1,('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$6),('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$7)),0))</f>
@@ -2889,16 +2886,16 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>9820</v>
+        <v>3610</v>
       </c>
       <c r="E14" t="n">
         <v>72</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>196</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H14" s="8">
         <f>IF($E14*'설정'!$C$5*IF(('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)&lt;1,('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$6),('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E14*'설정'!$C$5*IF(('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)&lt;1,('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$6),('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$7)),0))</f>
@@ -2971,21 +2968,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="6" t="n">
-        <v>13000</v>
+        <v>5500</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>93.8</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H15" s="8">
         <f>IF($E15*'설정'!$C$5*IF(('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)&lt;1,('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$6),('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E15*'설정'!$C$5*IF(('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)&lt;1,('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$6),('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$7)),0))</f>
@@ -3058,21 +3055,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="6" t="n">
-        <v>17100</v>
+        <v>4850</v>
       </c>
       <c r="E16" t="n">
         <v>72</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>342</v>
+        <v>97.02</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H16" s="8">
         <f>IF($E16*'설정'!$C$5*IF(('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)&lt;1,('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$6),('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E16*'설정'!$C$5*IF(('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)&lt;1,('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$6),('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$7)),0))</f>
@@ -3145,7 +3142,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3154,16 +3151,16 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>22600</v>
+        <v>6400</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>452</v>
+        <v>128</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="8">
         <f>IF($E17*'설정'!$C$5*IF(('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)&lt;1,('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$6),('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E17*'설정'!$C$5*IF(('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)&lt;1,('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$6),('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$7)),0))</f>
@@ -3236,21 +3233,21 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="9" t="n">
-        <v>39500</v>
+        <v>6380</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>790</v>
+        <v>128</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H18" s="8">
         <f>IF($E18*'설정'!$C$5*IF(('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)&lt;1,('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$6),('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E18*'설정'!$C$5*IF(('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)&lt;1,('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$6),('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$7)),0))</f>
@@ -3323,21 +3320,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="6" t="n">
-        <v>67200</v>
+        <v>7310</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1340</v>
+        <v>146</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H19" s="8">
         <f>IF($E19*'설정'!$C$5*IF(('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)&lt;1,('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$6),('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E19*'설정'!$C$5*IF(('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)&lt;1,('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$6),('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$7)),0))</f>
@@ -3415,16 +3412,16 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" s="6" t="n">
-        <v>141000</v>
+        <v>10900</v>
       </c>
       <c r="E20" t="n">
-        <v>108</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2820</v>
+        <v>218</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H20" s="8">
         <f>IF($E20*'설정'!$C$5*IF(('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)&lt;1,('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$6),('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E20*'설정'!$C$5*IF(('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)&lt;1,('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$6),('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$7)),0))</f>
@@ -3497,21 +3494,21 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="9" t="n">
-        <v>310000</v>
+        <v>9990</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6210</v>
+        <v>200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H21" s="8">
         <f>IF($E21*'설정'!$C$5*IF(('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)&lt;1,('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$6),('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E21*'설정'!$C$5*IF(('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)&lt;1,('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$6),('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$7)),0))</f>
@@ -3593,16 +3590,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>228000</v>
+        <v>13700</v>
       </c>
       <c r="E22" t="n">
         <v>90</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4570</v>
+        <v>274</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H22" s="8">
         <f>IF($E22*'설정'!$C$5*IF(('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)&lt;1,('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$6),('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E22*'설정'!$C$5*IF(('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)&lt;1,('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$6),('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$7)),0))</f>
@@ -3680,16 +3677,16 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="6" t="n">
-        <v>203000</v>
+        <v>14200</v>
       </c>
       <c r="E23" t="n">
         <v>72</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4060</v>
+        <v>284</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H23" s="8">
         <f>IF($E23*'설정'!$C$5*IF(('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)&lt;1,('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$6),('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E23*'설정'!$C$5*IF(('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)&lt;1,('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$6),('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$7)),0))</f>
@@ -3767,16 +3764,16 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" s="6" t="n">
-        <v>208000</v>
+        <v>16900</v>
       </c>
       <c r="E24" t="n">
         <v>72</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4160</v>
+        <v>338</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H24" s="8">
         <f>IF($E24*'설정'!$C$5*IF(('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)&lt;1,('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)^(-'설정'!$C$6),('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E24*'설정'!$C$5*IF(('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)&lt;1,('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)^(-'설정'!$C$6),('설정'!$C$22*IF($A24&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D24)^(-'설정'!$C$7)),0))</f>
@@ -3849,21 +3846,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="6" t="n">
-        <v>213000</v>
+        <v>26200</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4250</v>
+        <v>524</v>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H25" s="8">
         <f>IF($E25*'설정'!$C$5*IF(('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)&lt;1,('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$6),('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E25*'설정'!$C$5*IF(('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)&lt;1,('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$6),('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$7)),0))</f>
@@ -3936,21 +3933,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" s="6" t="n">
-        <v>218000</v>
+        <v>23600</v>
       </c>
       <c r="E26" t="n">
         <v>72</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4350</v>
+        <v>472</v>
       </c>
       <c r="G26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H26" s="8">
         <f>IF($E26*'설정'!$C$5*IF(('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)&lt;1,('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$6),('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E26*'설정'!$C$5*IF(('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)&lt;1,('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$6),('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$7)),0))</f>
@@ -4032,16 +4029,16 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>256000</v>
+        <v>31800</v>
       </c>
       <c r="E27" t="n">
         <v>90</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5120</v>
+        <v>636</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H27" s="8">
         <f>IF($E27*'설정'!$C$5*IF(('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)&lt;1,('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$6),('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E27*'설정'!$C$5*IF(('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)&lt;1,('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$6),('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$7)),0))</f>
@@ -4119,16 +4116,16 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" s="6" t="n">
-        <v>228000</v>
+        <v>32400</v>
       </c>
       <c r="E28" t="n">
         <v>72</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>4560</v>
+        <v>647</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H28" s="8">
         <f>IF($E28*'설정'!$C$5*IF(('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)&lt;1,('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$6),('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E28*'설정'!$C$5*IF(('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)&lt;1,('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$6),('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$7)),0))</f>
@@ -4206,16 +4203,16 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" s="6" t="n">
-        <v>233000</v>
+        <v>37900</v>
       </c>
       <c r="E29" t="n">
         <v>72</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4670</v>
+        <v>758</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H29" s="8">
         <f>IF($E29*'설정'!$C$5*IF(('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)&lt;1,('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$6),('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E29*'설정'!$C$5*IF(('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)&lt;1,('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$6),('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$7)),0))</f>
@@ -4288,21 +4285,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="6" t="n">
-        <v>239000</v>
+        <v>57700</v>
       </c>
       <c r="E30" t="n">
-        <v>72</v>
+        <v>110.6</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>4770</v>
+        <v>1150</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H30" s="8">
         <f>IF($E30*'설정'!$C$5*IF(('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)&lt;1,('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$6),('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E30*'설정'!$C$5*IF(('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)&lt;1,('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$6),('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$7)),0))</f>
@@ -4375,21 +4372,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" s="6" t="n">
-        <v>244000</v>
+        <v>56700</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4890</v>
+        <v>1130</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H31" s="8">
         <f>IF($E31*'설정'!$C$5*IF(('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)&lt;1,('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$6),('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E31*'설정'!$C$5*IF(('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)&lt;1,('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$6),('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$7)),0))</f>
@@ -4462,7 +4459,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -4471,16 +4468,16 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>400000</v>
+        <v>83400</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>8000</v>
+        <v>1670</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H32" s="8">
         <f>IF($E32*'설정'!$C$5*IF(('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)&lt;1,('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$6),('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E32*'설정'!$C$5*IF(('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)&lt;1,('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$6),('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$7)),0))</f>
@@ -4553,21 +4550,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="6" t="n">
-        <v>267000</v>
+        <v>92700</v>
       </c>
       <c r="E33" t="n">
         <v>72</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>5350</v>
+        <v>1850</v>
       </c>
       <c r="G33" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H33" s="8">
         <f>IF($E33*'설정'!$C$5*IF(('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)&lt;1,('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$6),('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E33*'설정'!$C$5*IF(('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)&lt;1,('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$6),('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$7)),0))</f>
@@ -4640,21 +4637,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="6" t="n">
-        <v>286000</v>
+        <v>119000</v>
       </c>
       <c r="E34" t="n">
         <v>72</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>5720</v>
+        <v>2370</v>
       </c>
       <c r="G34" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H34" s="8">
         <f>IF($E34*'설정'!$C$5*IF(('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)&lt;1,('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$6),('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E34*'설정'!$C$5*IF(('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)&lt;1,('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$6),('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$7)),0))</f>
@@ -4732,16 +4729,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="6" t="n">
-        <v>306000</v>
+        <v>151000</v>
       </c>
       <c r="E35" t="n">
         <v>72</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>6120</v>
+        <v>3030</v>
       </c>
       <c r="G35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H35" s="8">
         <f>IF($E35*'설정'!$C$5*IF(('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)&lt;1,('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$6),('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E35*'설정'!$C$5*IF(('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)&lt;1,('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$6),('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$7)),0))</f>
@@ -4814,21 +4811,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="6" t="n">
-        <v>327000</v>
+        <v>252000</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>117.6</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>6540</v>
+        <v>5030</v>
       </c>
       <c r="G36" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H36" s="8">
         <f>IF($E36*'설정'!$C$5*IF(('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)&lt;1,('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$6),('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E36*'설정'!$C$5*IF(('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)&lt;1,('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$6),('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$7)),0))</f>
@@ -4910,16 +4907,16 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>402000</v>
+        <v>247000</v>
       </c>
       <c r="E37" t="n">
         <v>90</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>8050</v>
+        <v>4930</v>
       </c>
       <c r="G37" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H37" s="8">
         <f>IF($E37*'설정'!$C$5*IF(('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)&lt;1,('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$6),('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E37*'설정'!$C$5*IF(('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)&lt;1,('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$6),('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$7)),0))</f>
@@ -4997,16 +4994,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="6" t="n">
-        <v>374000</v>
+        <v>237000</v>
       </c>
       <c r="E38" t="n">
         <v>72</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>7490</v>
+        <v>4750</v>
       </c>
       <c r="G38" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H38" s="8">
         <f>IF($E38*'설정'!$C$5*IF(('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)&lt;1,('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$6),('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E38*'설정'!$C$5*IF(('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)&lt;1,('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$6),('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$7)),0))</f>
@@ -5084,16 +5081,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="6" t="n">
-        <v>400000</v>
+        <v>263000</v>
       </c>
       <c r="E39" t="n">
         <v>72</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8010</v>
+        <v>5260</v>
       </c>
       <c r="G39" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H39" s="8">
         <f>IF($E39*'설정'!$C$5*IF(('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)&lt;1,('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$6),('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E39*'설정'!$C$5*IF(('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)&lt;1,('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$6),('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$7)),0))</f>
@@ -5171,16 +5168,16 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" s="6" t="n">
-        <v>428000</v>
+        <v>291000</v>
       </c>
       <c r="E40" t="n">
         <v>72</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>8570</v>
+        <v>5820</v>
       </c>
       <c r="G40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H40" s="8">
         <f>IF($E40*'설정'!$C$5*IF(('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)&lt;1,('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$6),('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E40*'설정'!$C$5*IF(('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)&lt;1,('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$6),('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$7)),0))</f>
@@ -5253,21 +5250,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" s="6" t="n">
-        <v>458000</v>
+        <v>322000</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>9160</v>
+        <v>6450</v>
       </c>
       <c r="G41" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H41" s="8">
         <f>IF($E41*'설정'!$C$5*IF(('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)&lt;1,('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$6),('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E41*'설정'!$C$5*IF(('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)&lt;1,('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$6),('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$7)),0))</f>
@@ -5349,13 +5346,13 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>784000</v>
+        <v>464000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>149.1</v>
+        <v>147</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>15700</v>
+        <v>9280</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>41</v>
@@ -5436,13 +5433,13 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" s="6" t="n">
-        <v>562000</v>
+        <v>378000</v>
       </c>
       <c r="E43" t="n">
         <v>72</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>11200</v>
+        <v>7550</v>
       </c>
       <c r="G43" t="n">
         <v>41</v>
@@ -5518,18 +5515,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" s="6" t="n">
-        <v>645000</v>
+        <v>399000</v>
       </c>
       <c r="E44" t="n">
         <v>72</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>12900</v>
+        <v>7990</v>
       </c>
       <c r="G44" t="n">
         <v>41</v>
@@ -5610,13 +5607,13 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" s="6" t="n">
-        <v>741000</v>
+        <v>422000</v>
       </c>
       <c r="E45" t="n">
         <v>72</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>14800</v>
+        <v>8450</v>
       </c>
       <c r="G45" t="n">
         <v>41</v>
@@ -5697,13 +5694,13 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" s="6" t="n">
-        <v>850000</v>
+        <v>447000</v>
       </c>
       <c r="E46" t="n">
         <v>72</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>17000</v>
+        <v>8930</v>
       </c>
       <c r="G46" t="n">
         <v>41</v>
@@ -5788,16 +5785,16 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1120000</v>
+        <v>543000</v>
       </c>
       <c r="E47" t="n">
         <v>90</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>22400</v>
+        <v>10900</v>
       </c>
       <c r="G47" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H47" s="8">
         <f>IF($E47*'설정'!$C$5*IF(('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)&lt;1,('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$6),('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E47*'설정'!$C$5*IF(('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)&lt;1,('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$6),('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$7)),0))</f>
@@ -5870,21 +5867,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" s="6" t="n">
-        <v>1120000</v>
+        <v>650000</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>22400</v>
+        <v>13000</v>
       </c>
       <c r="G48" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H48" s="8">
         <f>IF($E48*'설정'!$C$5*IF(('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)&lt;1,('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$6),('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E48*'설정'!$C$5*IF(('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)&lt;1,('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$6),('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$7)),0))</f>
@@ -5957,21 +5954,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" s="6" t="n">
-        <v>1290000</v>
+        <v>630000</v>
       </c>
       <c r="E49" t="n">
         <v>72</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>25700</v>
+        <v>12600</v>
       </c>
       <c r="G49" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H49" s="8">
         <f>IF($E49*'설정'!$C$5*IF(('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)&lt;1,('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$6),('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E49*'설정'!$C$5*IF(('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)&lt;1,('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$6),('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$7)),0))</f>
@@ -6049,16 +6046,16 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" s="6" t="n">
-        <v>1470000</v>
+        <v>794000</v>
       </c>
       <c r="E50" t="n">
         <v>72</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>29500</v>
+        <v>15900</v>
       </c>
       <c r="G50" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H50" s="8">
         <f>IF($E50*'설정'!$C$5*IF(('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)&lt;1,('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$6),('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E50*'설정'!$C$5*IF(('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)&lt;1,('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$6),('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$7)),0))</f>
@@ -6131,21 +6128,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" s="6" t="n">
-        <v>1690000</v>
+        <v>1000000</v>
       </c>
       <c r="E51" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>33900</v>
+        <v>20000</v>
       </c>
       <c r="G51" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H51" s="8">
         <f>IF($E51*'설정'!$C$5*IF(('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)&lt;1,('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$6),('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E51*'설정'!$C$5*IF(('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)&lt;1,('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$6),('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$7)),0))</f>
@@ -6218,7 +6215,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -6227,16 +6224,16 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>3110000</v>
+        <v>1450000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>151.2</v>
+        <v>90</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>62200</v>
+        <v>29000</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H52" s="8">
         <f>IF($E52*'설정'!$C$5*IF(('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)&lt;1,('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$6),('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E52*'설정'!$C$5*IF(('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)&lt;1,('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$6),('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$7)),0))</f>
@@ -6309,21 +6306,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" s="6" t="n">
-        <v>2100000</v>
+        <v>1590000</v>
       </c>
       <c r="E53" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>42100</v>
+        <v>31800</v>
       </c>
       <c r="G53" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H53" s="8">
         <f>IF($E53*'설정'!$C$5*IF(('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)&lt;1,('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$6),('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E53*'설정'!$C$5*IF(('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)&lt;1,('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$6),('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$7)),0))</f>
@@ -6396,21 +6393,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" s="6" t="n">
-        <v>2280000</v>
+        <v>2600000</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>45600</v>
+        <v>52100</v>
       </c>
       <c r="G54" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H54" s="8">
         <f>IF($E54*'설정'!$C$5*IF(('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)&lt;1,('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$6),('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E54*'설정'!$C$5*IF(('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)&lt;1,('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$6),('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$7)),0))</f>
@@ -6483,21 +6480,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" s="6" t="n">
-        <v>2470000</v>
+        <v>2290000</v>
       </c>
       <c r="E55" t="n">
         <v>72</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>49400</v>
+        <v>45800</v>
       </c>
       <c r="G55" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H55" s="8">
         <f>IF($E55*'설정'!$C$5*IF(('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)&lt;1,('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$6),('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E55*'설정'!$C$5*IF(('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)&lt;1,('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$6),('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$7)),0))</f>
@@ -6575,16 +6572,16 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" s="6" t="n">
-        <v>2670000</v>
+        <v>2610000</v>
       </c>
       <c r="E56" t="n">
         <v>72</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>53500</v>
+        <v>52300</v>
       </c>
       <c r="G56" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H56" s="8">
         <f>IF($E56*'설정'!$C$5*IF(('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)&lt;1,('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$6),('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E56*'설정'!$C$5*IF(('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)&lt;1,('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$6),('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$7)),0))</f>
@@ -6666,16 +6663,16 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3330000</v>
+        <v>3440000</v>
       </c>
       <c r="E57" t="n">
         <v>90</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>66600</v>
+        <v>68700</v>
       </c>
       <c r="G57" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H57" s="8">
         <f>IF($E57*'설정'!$C$5*IF(('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)&lt;1,('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$6),('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E57*'설정'!$C$5*IF(('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)&lt;1,('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$6),('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$7)),0))</f>
@@ -6753,16 +6750,16 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" s="6" t="n">
-        <v>3140000</v>
+        <v>3410000</v>
       </c>
       <c r="E58" t="n">
         <v>72</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>62800</v>
+        <v>68300</v>
       </c>
       <c r="G58" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H58" s="8">
         <f>IF($E58*'설정'!$C$5*IF(('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)&lt;1,('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$6),('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E58*'설정'!$C$5*IF(('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)&lt;1,('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$6),('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$7)),0))</f>
@@ -6840,16 +6837,16 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" s="6" t="n">
-        <v>3400000</v>
+        <v>3900000</v>
       </c>
       <c r="E59" t="n">
         <v>72</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>68000</v>
+        <v>78000</v>
       </c>
       <c r="G59" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H59" s="8">
         <f>IF($E59*'설정'!$C$5*IF(('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)&lt;1,('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$6),('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E59*'설정'!$C$5*IF(('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)&lt;1,('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$6),('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$7)),0))</f>
@@ -6922,21 +6919,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" s="6" t="n">
-        <v>3680000</v>
+        <v>5790000</v>
       </c>
       <c r="E60" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>73600</v>
+        <v>116000</v>
       </c>
       <c r="G60" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H60" s="8">
         <f>IF($E60*'설정'!$C$5*IF(('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)&lt;1,('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$6),('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E60*'설정'!$C$5*IF(('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)&lt;1,('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$6),('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$7)),0))</f>
@@ -7009,21 +7006,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" s="6" t="n">
-        <v>3990000</v>
+        <v>5240000</v>
       </c>
       <c r="E61" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>79800</v>
+        <v>105000</v>
       </c>
       <c r="G61" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H61" s="8">
         <f>IF($E61*'설정'!$C$5*IF(('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)&lt;1,('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$6),('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E61*'설정'!$C$5*IF(('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)&lt;1,('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$6),('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$7)),0))</f>
@@ -7096,7 +7093,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7105,16 +7102,16 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>6910000</v>
+        <v>7080000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>153.3</v>
+        <v>90</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>138000</v>
+        <v>142000</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H62" s="8">
         <f>IF($E62*'설정'!$C$5*IF(('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)&lt;1,('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$6),('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E62*'설정'!$C$5*IF(('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)&lt;1,('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$6),('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$7)),0))</f>
@@ -7187,21 +7184,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" s="6" t="n">
-        <v>4760000</v>
+        <v>7240000</v>
       </c>
       <c r="E63" t="n">
         <v>72</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>95100</v>
+        <v>145000</v>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H63" s="8">
         <f>IF($E63*'설정'!$C$5*IF(('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)&lt;1,('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$6),('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E63*'설정'!$C$5*IF(('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)&lt;1,('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$6),('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$7)),0))</f>
@@ -7274,21 +7271,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" s="6" t="n">
-        <v>5240000</v>
+        <v>8520000</v>
       </c>
       <c r="E64" t="n">
         <v>72</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>105000</v>
+        <v>170000</v>
       </c>
       <c r="G64" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H64" s="8">
         <f>IF($E64*'설정'!$C$5*IF(('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)&lt;1,('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)^(-'설정'!$C$6),('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E64*'설정'!$C$5*IF(('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)&lt;1,('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)^(-'설정'!$C$6),('설정'!$C$22*IF($A64&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D64)^(-'설정'!$C$7)),0))</f>
@@ -7366,16 +7363,16 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" s="6" t="n">
-        <v>5770000</v>
+        <v>10000000</v>
       </c>
       <c r="E65" t="n">
         <v>72</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="G65" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H65" s="8">
         <f>IF($E65*'설정'!$C$5*IF(('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)&lt;1,('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$6),('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E65*'설정'!$C$5*IF(('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)&lt;1,('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$6),('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$7)),0))</f>
@@ -7448,21 +7445,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" s="6" t="n">
-        <v>6350000</v>
+        <v>15300000</v>
       </c>
       <c r="E66" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>127000</v>
+        <v>306000</v>
       </c>
       <c r="G66" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H66" s="8">
         <f>IF($E66*'설정'!$C$5*IF(('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)&lt;1,('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$6),('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E66*'설정'!$C$5*IF(('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)&lt;1,('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$6),('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$7)),0))</f>
@@ -7544,16 +7541,16 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>8040000</v>
+        <v>14900000</v>
       </c>
       <c r="E67" t="n">
         <v>90</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>161000</v>
+        <v>299000</v>
       </c>
       <c r="G67" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H67" s="8">
         <f>IF($E67*'설정'!$C$5*IF(('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)&lt;1,('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$6),('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E67*'설정'!$C$5*IF(('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)&lt;1,('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$6),('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$7)),0))</f>
@@ -7631,16 +7628,16 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" s="6" t="n">
-        <v>7700000</v>
+        <v>14300000</v>
       </c>
       <c r="E68" t="n">
         <v>72</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>154000</v>
+        <v>286000</v>
       </c>
       <c r="G68" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H68" s="8">
         <f>IF($E68*'설정'!$C$5*IF(('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)&lt;1,('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$6),('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E68*'설정'!$C$5*IF(('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)&lt;1,('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$6),('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$7)),0))</f>
@@ -7718,16 +7715,16 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" s="6" t="n">
-        <v>8470000</v>
+        <v>15800000</v>
       </c>
       <c r="E69" t="n">
         <v>72</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>169000</v>
+        <v>315000</v>
       </c>
       <c r="G69" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H69" s="8">
         <f>IF($E69*'설정'!$C$5*IF(('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)&lt;1,('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$6),('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E69*'설정'!$C$5*IF(('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)&lt;1,('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$6),('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$7)),0))</f>
@@ -7805,16 +7802,16 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" s="6" t="n">
-        <v>9330000</v>
+        <v>17400000</v>
       </c>
       <c r="E70" t="n">
         <v>72</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>187000</v>
+        <v>348000</v>
       </c>
       <c r="G70" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H70" s="8">
         <f>IF($E70*'설정'!$C$5*IF(('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)&lt;1,('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)^(-'설정'!$C$6),('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E70*'설정'!$C$5*IF(('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)&lt;1,('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)^(-'설정'!$C$6),('설정'!$C$22*IF($A70&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D70)^(-'설정'!$C$7)),0))</f>
@@ -7887,21 +7884,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" s="6" t="n">
-        <v>10300000</v>
+        <v>19200000</v>
       </c>
       <c r="E71" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>205000</v>
+        <v>383000</v>
       </c>
       <c r="G71" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H71" s="8">
         <f>IF($E71*'설정'!$C$5*IF(('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)&lt;1,('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$6),('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E71*'설정'!$C$5*IF(('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)&lt;1,('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$6),('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$7)),0))</f>
@@ -7983,13 +7980,13 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>18100000</v>
+        <v>27500000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>155.4</v>
+        <v>157.5</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>362000</v>
+        <v>549000</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>71</v>
@@ -8070,13 +8067,13 @@
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" s="6" t="n">
-        <v>12000000</v>
+        <v>22400000</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>240000</v>
+        <v>448000</v>
       </c>
       <c r="G73" t="n">
         <v>71</v>
@@ -8152,18 +8149,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" s="6" t="n">
-        <v>12700000</v>
+        <v>23700000</v>
       </c>
       <c r="E74" t="n">
         <v>72</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>254000</v>
+        <v>475000</v>
       </c>
       <c r="G74" t="n">
         <v>71</v>
@@ -8244,13 +8241,13 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" s="6" t="n">
-        <v>13500000</v>
+        <v>25200000</v>
       </c>
       <c r="E75" t="n">
         <v>72</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>270000</v>
+        <v>503000</v>
       </c>
       <c r="G75" t="n">
         <v>71</v>
@@ -8331,13 +8328,13 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" s="6" t="n">
-        <v>14300000</v>
+        <v>26700000</v>
       </c>
       <c r="E76" t="n">
         <v>72</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>286000</v>
+        <v>534000</v>
       </c>
       <c r="G76" t="n">
         <v>71</v>
@@ -8422,16 +8419,16 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>17400000</v>
+        <v>32500000</v>
       </c>
       <c r="E77" t="n">
         <v>90</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>348000</v>
+        <v>650000</v>
       </c>
       <c r="G77" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H77" s="8">
         <f>IF($E77*'설정'!$C$5*IF(('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)&lt;1,('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$6),('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E77*'설정'!$C$5*IF(('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)&lt;1,('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$6),('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$7)),0))</f>
@@ -8509,16 +8506,16 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" s="6" t="n">
-        <v>16100000</v>
+        <v>30000000</v>
       </c>
       <c r="E78" t="n">
         <v>72</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>321000</v>
+        <v>600000</v>
       </c>
       <c r="G78" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="8">
         <f>IF($E78*'설정'!$C$5*IF(('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)&lt;1,('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$6),('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E78*'설정'!$C$5*IF(('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)&lt;1,('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$6),('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$7)),0))</f>
@@ -8591,21 +8588,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" s="6" t="n">
-        <v>17000000</v>
+        <v>41300000</v>
       </c>
       <c r="E79" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>340000</v>
+        <v>826000</v>
       </c>
       <c r="G79" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H79" s="8">
         <f>IF($E79*'설정'!$C$5*IF(('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)&lt;1,('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$6),('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E79*'설정'!$C$5*IF(('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)&lt;1,('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$6),('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$7)),0))</f>
@@ -8678,21 +8675,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" s="6" t="n">
-        <v>18000000</v>
+        <v>33600000</v>
       </c>
       <c r="E80" t="n">
         <v>72</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>361000</v>
+        <v>671000</v>
       </c>
       <c r="G80" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H80" s="8">
         <f>IF($E80*'설정'!$C$5*IF(('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)&lt;1,('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$6),('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E80*'설정'!$C$5*IF(('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)&lt;1,('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$6),('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$7)),0))</f>
@@ -8765,21 +8762,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" s="6" t="n">
-        <v>19100000</v>
+        <v>35400000</v>
       </c>
       <c r="E81" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>383000</v>
+        <v>709000</v>
       </c>
       <c r="G81" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H81" s="8">
         <f>IF($E81*'설정'!$C$5*IF(('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)&lt;1,('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$6),('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E81*'설정'!$C$5*IF(('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)&lt;1,('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$6),('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$7)),0))</f>
@@ -8852,7 +8849,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8861,16 +8858,16 @@
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>32400000</v>
+        <v>43000000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>157.5</v>
+        <v>90</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>649000</v>
+        <v>861000</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H82" s="8">
         <f>IF($E82*'설정'!$C$5*IF(('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)&lt;1,('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$6),('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E82*'설정'!$C$5*IF(('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)&lt;1,('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$6),('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$7)),0))</f>
@@ -8943,21 +8940,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" s="6" t="n">
-        <v>21100000</v>
+        <v>39500000</v>
       </c>
       <c r="E83" t="n">
         <v>72</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>423000</v>
+        <v>790000</v>
       </c>
       <c r="G83" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H83" s="8">
         <f>IF($E83*'설정'!$C$5*IF(('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)&lt;1,('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$6),('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E83*'설정'!$C$5*IF(('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)&lt;1,('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$6),('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$7)),0))</f>
@@ -9030,21 +9027,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" s="6" t="n">
-        <v>22000000</v>
+        <v>41700000</v>
       </c>
       <c r="E84" t="n">
         <v>72</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>440000</v>
+        <v>834000</v>
       </c>
       <c r="G84" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H84" s="8">
         <f>IF($E84*'설정'!$C$5*IF(('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)&lt;1,('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$6),('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E84*'설정'!$C$5*IF(('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)&lt;1,('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$6),('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$7)),0))</f>
@@ -9122,16 +9119,16 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" s="6" t="n">
-        <v>22900000</v>
+        <v>44000000</v>
       </c>
       <c r="E85" t="n">
         <v>72</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>459000</v>
+        <v>881000</v>
       </c>
       <c r="G85" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" s="8">
         <f>IF($E85*'설정'!$C$5*IF(('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)&lt;1,('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$6),('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E85*'설정'!$C$5*IF(('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)&lt;1,('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$6),('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$7)),0))</f>
@@ -9204,21 +9201,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" s="6" t="n">
-        <v>23900000</v>
+        <v>60500000</v>
       </c>
       <c r="E86" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>478000</v>
+        <v>1210000</v>
       </c>
       <c r="G86" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H86" s="8">
         <f>IF($E86*'설정'!$C$5*IF(('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)&lt;1,('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$6),('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E86*'설정'!$C$5*IF(('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)&lt;1,('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$6),('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$7)),0))</f>
@@ -9300,16 +9297,16 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>28600000</v>
+        <v>56200000</v>
       </c>
       <c r="E87" t="n">
         <v>90</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>572000</v>
+        <v>1120000</v>
       </c>
       <c r="G87" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H87" s="8">
         <f>IF($E87*'설정'!$C$5*IF(('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)&lt;1,('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$6),('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E87*'설정'!$C$5*IF(('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)&lt;1,('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$6),('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$7)),0))</f>
@@ -9387,16 +9384,16 @@
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" s="6" t="n">
-        <v>25900000</v>
+        <v>51300000</v>
       </c>
       <c r="E88" t="n">
         <v>72</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>518000</v>
+        <v>1030000</v>
       </c>
       <c r="G88" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H88" s="8">
         <f>IF($E88*'설정'!$C$5*IF(('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)&lt;1,('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$6),('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E88*'설정'!$C$5*IF(('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)&lt;1,('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$6),('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$7)),0))</f>
@@ -9474,16 +9471,16 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" s="6" t="n">
-        <v>27000000</v>
+        <v>53900000</v>
       </c>
       <c r="E89" t="n">
         <v>72</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>540000</v>
+        <v>1080000</v>
       </c>
       <c r="G89" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H89" s="8">
         <f>IF($E89*'설정'!$C$5*IF(('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)&lt;1,('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$6),('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E89*'설정'!$C$5*IF(('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)&lt;1,('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$6),('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$7)),0))</f>
@@ -9561,16 +9558,16 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" s="6" t="n">
-        <v>28100000</v>
+        <v>56600000</v>
       </c>
       <c r="E90" t="n">
         <v>72</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>562000</v>
+        <v>1130000</v>
       </c>
       <c r="G90" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H90" s="8">
         <f>IF($E90*'설정'!$C$5*IF(('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)&lt;1,('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$6),('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E90*'설정'!$C$5*IF(('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)&lt;1,('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$6),('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$7)),0))</f>
@@ -9643,21 +9640,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" s="6" t="n">
-        <v>29300000</v>
+        <v>59500000</v>
       </c>
       <c r="E91" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>586000</v>
+        <v>1190000</v>
       </c>
       <c r="G91" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H91" s="8">
         <f>IF($E91*'설정'!$C$5*IF(('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)&lt;1,('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)^(-'설정'!$C$6),('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E91*'설정'!$C$5*IF(('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)&lt;1,('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)^(-'설정'!$C$6),('설정'!$C$22*IF($A91&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D91)^(-'설정'!$C$7)),0))</f>
@@ -9730,7 +9727,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9739,16 +9736,16 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>48800000</v>
+        <v>71800000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>159.6</v>
+        <v>90</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>977000</v>
+        <v>1440000</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H92" s="8">
         <f>IF($E92*'설정'!$C$5*IF(('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)&lt;1,('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$6),('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E92*'설정'!$C$5*IF(('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)&lt;1,('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$6),('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$7)),0))</f>
@@ -9821,21 +9818,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" s="6" t="n">
-        <v>31700000</v>
+        <v>65600000</v>
       </c>
       <c r="E93" t="n">
         <v>72</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>634000</v>
+        <v>1310000</v>
       </c>
       <c r="G93" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H93" s="8">
         <f>IF($E93*'설정'!$C$5*IF(('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)&lt;1,('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$6),('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E93*'설정'!$C$5*IF(('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)&lt;1,('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$6),('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$7)),0))</f>
@@ -9908,21 +9905,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" s="6" t="n">
-        <v>32900000</v>
+        <v>89600000</v>
       </c>
       <c r="E94" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>659000</v>
+        <v>1790000</v>
       </c>
       <c r="G94" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H94" s="8">
         <f>IF($E94*'설정'!$C$5*IF(('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)&lt;1,('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$6),('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E94*'설정'!$C$5*IF(('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)&lt;1,('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$6),('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$7)),0))</f>
@@ -9995,21 +9992,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" s="6" t="n">
-        <v>34200000</v>
+        <v>71000000</v>
       </c>
       <c r="E95" t="n">
         <v>72</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>684000</v>
+        <v>1420000</v>
       </c>
       <c r="G95" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H95" s="8">
         <f>IF($E95*'설정'!$C$5*IF(('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)&lt;1,('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$6),('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E95*'설정'!$C$5*IF(('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)&lt;1,('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$6),('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$7)),0))</f>
@@ -10091,16 +10088,16 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>40900000</v>
+        <v>84100000</v>
       </c>
       <c r="E96" t="n">
         <v>90</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>817000</v>
+        <v>1680000</v>
       </c>
       <c r="G96" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H96" s="8">
         <f>IF($E96*'설정'!$C$5*IF(('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)&lt;1,('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$6),('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E96*'설정'!$C$5*IF(('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)&lt;1,('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$6),('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$7)),0))</f>
@@ -10178,16 +10175,16 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" s="6" t="n">
-        <v>36900000</v>
+        <v>75300000</v>
       </c>
       <c r="E97" t="n">
         <v>72</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>738000</v>
+        <v>1510000</v>
       </c>
       <c r="G97" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H97" s="8">
         <f>IF($E97*'설정'!$C$5*IF(('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)&lt;1,('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$6),('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E97*'설정'!$C$5*IF(('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)&lt;1,('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$6),('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$7)),0))</f>
@@ -10265,16 +10262,16 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" s="6" t="n">
-        <v>38300000</v>
+        <v>77600000</v>
       </c>
       <c r="E98" t="n">
         <v>72</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>767000</v>
+        <v>1550000</v>
       </c>
       <c r="G98" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H98" s="8">
         <f>IF($E98*'설정'!$C$5*IF(('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)&lt;1,('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$6),('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E98*'설정'!$C$5*IF(('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)&lt;1,('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$6),('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$7)),0))</f>
@@ -10356,16 +10353,16 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>45800000</v>
+        <v>91900000</v>
       </c>
       <c r="E99" t="n">
         <v>90</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>916000</v>
+        <v>1840000</v>
       </c>
       <c r="G99" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H99" s="8">
         <f>IF($E99*'설정'!$C$5*IF(('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)&lt;1,('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$6),('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E99*'설정'!$C$5*IF(('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)&lt;1,('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$6),('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$7)),0))</f>
@@ -10443,16 +10440,16 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" s="6" t="n">
-        <v>41400000</v>
+        <v>82300000</v>
       </c>
       <c r="E100" t="n">
         <v>72</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>828000</v>
+        <v>1650000</v>
       </c>
       <c r="G100" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H100" s="8">
         <f>IF($E100*'설정'!$C$5*IF(('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)&lt;1,('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$6),('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E100*'설정'!$C$5*IF(('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)&lt;1,('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$6),('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$7)),0))</f>
@@ -10525,21 +10522,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" s="6" t="n">
-        <v>43000000</v>
+        <v>84800000</v>
       </c>
       <c r="E101" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>860000</v>
+        <v>1700000</v>
       </c>
       <c r="G101" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H101" s="8">
         <f>IF($E101*'설정'!$C$5*IF(('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)&lt;1,('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$6),('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E101*'설정'!$C$5*IF(('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)&lt;1,('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$6),('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$7)),0))</f>
@@ -10612,7 +10609,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -10621,16 +10618,16 @@
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>71400000</v>
+        <v>122000000</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>161.7</v>
+        <v>90</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>1430000</v>
+        <v>2440000</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H102" s="8">
         <f>IF($E102*'설정'!$C$5*IF(('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)&lt;1,('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$6),('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E102*'설정'!$C$5*IF(('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)&lt;1,('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$6),('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$7)),0))</f>
@@ -10719,7 +10716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10801,22 +10798,22 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>46.12</v>
+        <v>31.21</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>68737.80350201546</v>
+        <v>32204.07185943312</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>13</v>
@@ -10827,13 +10824,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.62</v>
+        <v>0.32</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -10845,13 +10842,13 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>92.23999999999999</v>
+        <v>79.88</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>72575.60700403093</v>
+        <v>76397.02943566462</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
@@ -10865,31 +10862,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>203.6</v>
+        <v>255.69</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>321664.496634864</v>
+        <v>746259.9413222184</v>
       </c>
       <c r="K4" t="n">
         <v>14</v>
@@ -10903,37 +10900,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>10.3</v>
+        <v>14.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>345.9699999999999</v>
+        <v>430.58</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>935651.2420423145</v>
+        <v>5295268.189350614</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -10941,37 +10938,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>212.0299999999999</v>
+        <v>406.35</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1506068.094864116</v>
+        <v>13612379.50113069</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -10979,37 +10976,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>278.3599999999999</v>
+        <v>461.86</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>2747394.398063242</v>
+        <v>26379454.91467971</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -11017,37 +11014,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>383.6899999999999</v>
+        <v>255.3699999999999</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>6247502.544789691</v>
+        <v>33436530.32822873</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -11055,37 +11052,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>9.9</v>
+        <v>15</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>507.8999999999999</v>
+        <v>745.8799999999999</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>9591089.408451859</v>
+        <v>108336448.7079646</v>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -11093,37 +11090,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H10" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>925.9899999999998</v>
+        <v>1063.88</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>31295600.22396451</v>
+        <v>227426263.8683756</v>
       </c>
       <c r="K10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -11131,37 +11128,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>1511.38</v>
+        <v>568.8799999999999</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>66375396.71942301</v>
+        <v>249916079.0287865</v>
       </c>
       <c r="K11" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -11169,34 +11166,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4</v>
+        <v>17.2</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>1605.77</v>
+        <v>2075.38</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>115780464.673584</v>
+        <v>1295457628.58637</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L12" t="n">
         <v>46</v>
@@ -11207,7 +11204,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
@@ -11216,28 +11213,28 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H13" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>2822.77</v>
+        <v>2877.88</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>200406938.9514939</v>
+        <v>2207399206.542687</v>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -11245,34 +11242,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>10.8</v>
+        <v>12.9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>1910.27</v>
+        <v>2418.38</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>310723356.6610337</v>
+        <v>3654238978.611913</v>
       </c>
       <c r="K14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L14" t="n">
         <v>52</v>
@@ -11283,7 +11280,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
@@ -11292,28 +11289,28 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H15" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>3177.77</v>
+        <v>3863.38</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>551839774.3705735</v>
+        <v>8690862409.628456</v>
       </c>
       <c r="K15" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -11321,37 +11318,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2.33</v>
+        <v>2.61</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H16" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>1948.27</v>
+        <v>7373.38</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>590456192.0801133</v>
+        <v>16402485840.645</v>
       </c>
       <c r="K16" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -11359,7 +11356,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.49</v>
+        <v>2.81</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
@@ -11368,28 +11365,28 @@
         <v>0.35</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>11.9</v>
+        <v>10.3</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>3716.77</v>
+        <v>5192.38</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>882270194.2044327</v>
+        <v>18321529081.40352</v>
       </c>
       <c r="K17" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="L17" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -11397,37 +11394,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H18" t="n">
-        <v>10.4</v>
+        <v>21.2</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>4907.27</v>
+        <v>20762.38</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>920084196.3287522</v>
+        <v>53709495384.35252</v>
       </c>
       <c r="K18" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="L18" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -11435,37 +11432,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.86</v>
+        <v>3.33</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H19" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>6069.77</v>
+        <v>27135.38</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>927898198.4530716</v>
+        <v>70497308183.71701</v>
       </c>
       <c r="K19" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="L19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -11473,37 +11470,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" t="n">
-        <v>24.7</v>
+        <v>18.6</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>33371.27</v>
+        <v>38239.38</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>27330918154.54673</v>
+        <v>138746469952.0185</v>
       </c>
       <c r="K20" t="n">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="L20" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -11511,37 +11508,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.43</v>
+        <v>3.81</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>31636.27</v>
+        <v>65710.38</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>26082014910.21689</v>
+        <v>217937871910.4391</v>
       </c>
       <c r="K21" t="n">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -11549,37 +11546,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3.69</v>
+        <v>4.08</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>28.5</v>
+        <v>9.9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>77953.26999999999</v>
+        <v>30067.38</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>125033092406.4033</v>
+        <v>171802521881.4778</v>
       </c>
       <c r="K22" t="n">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="L22" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -11587,37 +11584,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H23" t="n">
-        <v>32.9</v>
+        <v>9.9</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>116262.27</v>
+        <v>54317.38</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>306979681481.2426</v>
+        <v>274567171852.5165</v>
       </c>
       <c r="K23" t="n">
-        <v>281</v>
+        <v>197</v>
       </c>
       <c r="L23" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
@@ -11625,34 +11622,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>4.71</v>
+        <v>4.41</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H24" t="n">
-        <v>25.1</v>
+        <v>13.9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>109574.27</v>
+        <v>55222.38</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>363688711277.6649</v>
+        <v>463414213532.0444</v>
       </c>
       <c r="K24" t="n">
-        <v>312</v>
+        <v>203</v>
       </c>
       <c r="L24" t="n">
         <v>87</v>
@@ -11663,34 +11660,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>5.13</v>
+        <v>4.65</v>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H25" t="n">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>79621.26999999999</v>
+        <v>51117.38</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>552805887610.5625</v>
+        <v>368187445785.2077</v>
       </c>
       <c r="K25" t="n">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="L25" t="n">
         <v>87</v>
@@ -11701,37 +11698,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>5.42</v>
+        <v>4.79</v>
       </c>
       <c r="C26" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.35</v>
+        <v>0.95</v>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H26" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>97326.26999999999</v>
+        <v>233515.38</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>479260121750.9578</v>
+        <v>1167179711253.314</v>
       </c>
       <c r="K26" t="n">
-        <v>332</v>
+        <v>228</v>
       </c>
       <c r="L26" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
@@ -11739,37 +11736,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>5.68</v>
+        <v>5.09</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="E27" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H27" t="n">
-        <v>13.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>116835.27</v>
+        <v>136258.38</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>417714355891.3531</v>
+        <v>1426983134588.229</v>
       </c>
       <c r="K27" t="n">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="L27" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
@@ -11777,37 +11774,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>5.9</v>
+        <v>5.26</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F28" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H28" t="n">
-        <v>29.3</v>
+        <v>21.5</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>416560.27</v>
+        <v>581135.38</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>1707215042565.656</v>
+        <v>3893122900611.269</v>
       </c>
       <c r="K28" t="n">
-        <v>375</v>
+        <v>282</v>
       </c>
       <c r="L28" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29">
@@ -11815,37 +11812,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>6.39</v>
+        <v>5.62</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="E29" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H29" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>586297.27</v>
+        <v>341934.38</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>2443963619077.259</v>
+        <v>4534718557895.381</v>
       </c>
       <c r="K29" t="n">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="L29" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
@@ -11853,37 +11850,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>6.67</v>
+        <v>5.79</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="E30" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>22.5</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>270773.27</v>
+        <v>1309789.38</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>1805712195588.861</v>
+        <v>10375017327010.46</v>
       </c>
       <c r="K30" t="n">
-        <v>417</v>
+        <v>316</v>
       </c>
       <c r="L30" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -11891,16 +11888,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>6.9</v>
+        <v>6.17</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
         <v>69</v>
@@ -11909,19 +11906,19 @@
         <v>70</v>
       </c>
       <c r="H31" t="n">
-        <v>30.8</v>
+        <v>11.3</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1052163.27</v>
+        <v>1539386.38</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>5741555074461.725</v>
+        <v>11640782706026.4</v>
       </c>
       <c r="K31" t="n">
-        <v>457</v>
+        <v>322</v>
       </c>
       <c r="L31" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
@@ -11929,37 +11926,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>7.42</v>
+        <v>6.36</v>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F32" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H32" t="n">
-        <v>16.9</v>
+        <v>21.3</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>681894.27</v>
+        <v>2552452.38</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>7614543962854.43</v>
+        <v>26179907981329.03</v>
       </c>
       <c r="K32" t="n">
-        <v>483</v>
+        <v>374</v>
       </c>
       <c r="L32" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
@@ -11967,37 +11964,37 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>7.7</v>
+        <v>6.71</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>21.6</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>671909.27</v>
+        <v>3940690.38</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>5407532851247.135</v>
+        <v>48960835695510.09</v>
       </c>
       <c r="K33" t="n">
-        <v>490</v>
+        <v>421</v>
       </c>
       <c r="L33" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
@@ -12005,37 +12002,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7.93</v>
+        <v>7.07</v>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F34" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G34" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H34" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>2142830.27</v>
+        <v>6443846.38</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>14022323001653.41</v>
+        <v>90166159383421.55</v>
       </c>
       <c r="K34" t="n">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="L34" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
@@ -12043,37 +12040,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>8.359999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F35" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G35" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H35" t="n">
-        <v>15.8</v>
+        <v>10.7</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>2807398.27</v>
+        <v>6073155.38</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>17082753292624.49</v>
+        <v>76805396941473.47</v>
       </c>
       <c r="K35" t="n">
-        <v>542</v>
+        <v>471</v>
       </c>
       <c r="L35" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -12081,263 +12078,35 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>8.619999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F36" t="n">
-        <v>89</v>
-      </c>
-      <c r="G36" t="n">
-        <v>90</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>29.3</v>
+        <v>17.4</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>4025352.27</v>
+        <v>10869011.38</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>36628974086042.45</v>
+        <v>150276757290166.8</v>
       </c>
       <c r="K36" t="n">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="L36" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="C37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>81</v>
-      </c>
-      <c r="F37" t="n">
-        <v>89</v>
-      </c>
-      <c r="G37" t="n">
-        <v>90</v>
-      </c>
-      <c r="H37" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>4069465.27</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>29918429148403.88</v>
-      </c>
-      <c r="K37" t="n">
-        <v>608</v>
-      </c>
-      <c r="L37" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="C38" t="n">
-        <v>14</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E38" t="n">
-        <v>81</v>
-      </c>
-      <c r="F38" t="n">
-        <v>99</v>
-      </c>
-      <c r="G38" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>6281445.27</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>72160178577421.56</v>
-      </c>
-      <c r="K38" t="n">
-        <v>655</v>
-      </c>
-      <c r="L38" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="C39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>91</v>
-      </c>
-      <c r="F39" t="n">
-        <v>99</v>
-      </c>
-      <c r="G39" t="n">
-        <v>100</v>
-      </c>
-      <c r="H39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>5699431.27</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>52617622722621.75</v>
-      </c>
-      <c r="K39" t="n">
-        <v>672</v>
-      </c>
-      <c r="L39" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="C40" t="n">
-        <v>14</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>91</v>
-      </c>
-      <c r="F40" t="n">
-        <v>99</v>
-      </c>
-      <c r="G40" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>9150931.27</v>
-      </c>
-      <c r="J40" s="11" t="n">
-        <v>83675066867821.94</v>
-      </c>
-      <c r="K40" t="n">
-        <v>686</v>
-      </c>
-      <c r="L40" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="C41" t="n">
-        <v>14</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>91</v>
-      </c>
-      <c r="F41" t="n">
-        <v>99</v>
-      </c>
-      <c r="G41" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>12602431.27</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>114732511013022.1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>704</v>
-      </c>
-      <c r="L41" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="C42" t="n">
-        <v>15</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E42" t="n">
-        <v>95</v>
-      </c>
-      <c r="F42" t="n">
-        <v>100</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>2891285.27</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>36097773463207.44</v>
-      </c>
-      <c r="K42" t="n">
-        <v>715</v>
-      </c>
-      <c r="L42" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -12351,7 +12120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12439,13 +12208,13 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>30.5</v>
+        <v>31.21</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>29771.71692980331</v>
+        <v>32204.07185943312</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -12459,7 +12228,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -12477,13 +12246,13 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>76.62</v>
+        <v>79.88</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>70609.52043181878</v>
+        <v>76397.02943566462</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
@@ -12497,7 +12266,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -12515,13 +12284,13 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>122.74</v>
+        <v>128.55</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>70847.32393383424</v>
+        <v>76589.98701189613</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
@@ -12535,7 +12304,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -12547,19 +12316,19 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>11.1</v>
+        <v>13.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>234.1</v>
+        <v>304.36</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>341636.2135646673</v>
+        <v>771752.8988984498</v>
       </c>
       <c r="K5" t="n">
         <v>14</v>
@@ -12573,31 +12342,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.08</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>95.45999999999998</v>
+        <v>219.5</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>586306.9441824585</v>
+        <v>663086.7267105276</v>
       </c>
       <c r="K6" t="n">
         <v>14</v>
@@ -12611,31 +12380,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.46</v>
+        <v>0.89</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>10.2</v>
+        <v>14.7</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>146.83</v>
+        <v>504.39</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>741093.6895899089</v>
+        <v>5369594.974738923</v>
       </c>
       <c r="K7" t="n">
         <v>23</v>
@@ -12649,37 +12418,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>201.39</v>
+        <v>289.14</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>1200097.162432338</v>
+        <v>4691852.033682284</v>
       </c>
       <c r="K8" t="n">
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -12687,37 +12456,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>9.300000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>304.3299999999999</v>
+        <v>552.525</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>1966867.005379118</v>
+        <v>22072319.41833667</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -12725,37 +12494,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>266.6599999999999</v>
+        <v>269.035</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>3082193.308578244</v>
+        <v>20329394.83188569</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -12763,37 +12532,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>379.8699999999999</v>
+        <v>557.545</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>4353847.064281438</v>
+        <v>47186083.57677385</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -12801,37 +12570,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>737.0799999999999</v>
+        <v>706.545</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>10634433.92794361</v>
+        <v>101658963.4210624</v>
       </c>
       <c r="K12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -12839,37 +12608,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
-        <v>13.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>995.1699999999998</v>
+        <v>1085.545</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>27678944.74345626</v>
+        <v>181531843.2653509</v>
       </c>
       <c r="K13" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -12877,34 +12646,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>12.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>1144.56</v>
+        <v>561.5450000000001</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>64008741.23891476</v>
+        <v>193021658.4257619</v>
       </c>
       <c r="K14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" t="n">
         <v>44</v>
@@ -12915,34 +12684,34 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="n">
         <v>9</v>
       </c>
-      <c r="F15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16</v>
-      </c>
-      <c r="H15" t="n">
-        <v>10.7</v>
-      </c>
       <c r="I15" s="11" t="n">
-        <v>1663.95</v>
+        <v>652.5450000000001</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>106023809.1930758</v>
+        <v>158911473.5861729</v>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L15" t="n">
         <v>46</v>
@@ -12953,37 +12722,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H16" t="n">
-        <v>11.3</v>
+        <v>19</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>1172.45</v>
+        <v>2364.045</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>140524506.4574744</v>
+        <v>1285053023.143756</v>
       </c>
       <c r="K16" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -12991,37 +12760,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.86</v>
+        <v>0.24</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H17" t="n">
-        <v>12.9</v>
+        <v>10.2</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1919.95</v>
+        <v>1302.545</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>333440924.1670142</v>
+        <v>1752994601.100073</v>
       </c>
       <c r="K17" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -13029,37 +12798,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>12.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>3079.45</v>
+        <v>1308.045</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>564557341.876554</v>
+        <v>1233936179.05639</v>
       </c>
       <c r="K18" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="L18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -13067,37 +12836,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.14</v>
+        <v>0.89</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>11.3</v>
+        <v>13.2</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1849.95</v>
+        <v>2887.545</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>603173759.5860938</v>
+        <v>3063775951.125617</v>
       </c>
       <c r="K19" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L19" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -13105,37 +12874,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.18</v>
+        <v>3.29</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>2208.45</v>
+        <v>3579.545</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>309790177.2956336</v>
+        <v>5254553401.474928</v>
       </c>
       <c r="K20" t="n">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L20" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -13143,37 +12912,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H21" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>3428.95</v>
+        <v>4979.545</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>362406595.0051733</v>
+        <v>8345330851.82424</v>
       </c>
       <c r="K21" t="n">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="L21" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -13181,37 +12950,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="C22" t="n">
         <v>7</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.51</v>
+        <v>0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H22" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>5999.45</v>
+        <v>3707.545</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>970220597.1294928</v>
+        <v>13696954282.84078</v>
       </c>
       <c r="K22" t="n">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="L22" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -13219,37 +12988,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H23" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>7149.95</v>
+        <v>5108.545</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>968034599.2538122</v>
+        <v>14015997523.5993</v>
       </c>
       <c r="K23" t="n">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="L23" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
@@ -13257,37 +13026,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H24" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>8216.450000000001</v>
+        <v>5368.545</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>945848601.3781316</v>
+        <v>11581675743.29689</v>
       </c>
       <c r="K24" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -13295,37 +13064,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="C25" t="n">
         <v>7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>36238.95</v>
+        <v>22585.545</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>27658868557.47179</v>
+        <v>52339642046.24589</v>
       </c>
       <c r="K25" t="n">
-        <v>227</v>
+        <v>148</v>
       </c>
       <c r="L25" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -13333,37 +13102,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>4.61</v>
+        <v>4.46</v>
       </c>
       <c r="C26" t="n">
         <v>8</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>35178.95</v>
+        <v>11563.545</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>26679965313.14195</v>
+        <v>67507454845.61037</v>
       </c>
       <c r="K26" t="n">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="L26" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -13371,37 +13140,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>4.92</v>
+        <v>4.64</v>
       </c>
       <c r="C27" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" t="n">
-        <v>18.4</v>
+        <v>20.5</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>44990.95</v>
+        <v>38041.545</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>28001062068.81211</v>
+        <v>126456616613.9118</v>
       </c>
       <c r="K27" t="n">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="L27" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28">
@@ -13409,37 +13178,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>5.23</v>
+        <v>4.98</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>55662.95</v>
+        <v>18148.545</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>30822158824.48227</v>
+        <v>137095354773.7277</v>
       </c>
       <c r="K28" t="n">
-        <v>273</v>
+        <v>196</v>
       </c>
       <c r="L28" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
@@ -13447,37 +13216,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>5.53</v>
+        <v>5.15</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H29" t="n">
-        <v>17.6</v>
+        <v>19.3</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>64402.95</v>
+        <v>49161.545</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>29743255580.15244</v>
+        <v>224239075045.3708</v>
       </c>
       <c r="K29" t="n">
-        <v>290</v>
+        <v>212</v>
       </c>
       <c r="L29" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
@@ -13485,34 +13254,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H30" t="n">
-        <v>31.9</v>
+        <v>11.5</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>109779.95</v>
+        <v>63778.545</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>126694333076.3389</v>
+        <v>283603725016.4095</v>
       </c>
       <c r="K30" t="n">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="L30" t="n">
         <v>87</v>
@@ -13523,37 +13292,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>6.36</v>
+        <v>5.67</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H31" t="n">
-        <v>20.3</v>
+        <v>15.1</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>64598.95</v>
+        <v>55459.545</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>113690594369.711</v>
+        <v>416450766695.9373</v>
       </c>
       <c r="K31" t="n">
-        <v>333</v>
+        <v>229</v>
       </c>
       <c r="L31" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
@@ -13561,37 +13330,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>6.69</v>
+        <v>5.92</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="E32" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G32" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H32" t="n">
-        <v>34.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>140892.95</v>
+        <v>49700.545</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>309237183444.5503</v>
+        <v>311223998949.1006</v>
       </c>
       <c r="K32" t="n">
-        <v>364</v>
+        <v>233</v>
       </c>
       <c r="L32" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
@@ -13599,37 +13368,37 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>7.28</v>
+        <v>6.08</v>
       </c>
       <c r="C33" t="n">
         <v>10</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G33" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H33" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>81784.95000000001</v>
+        <v>231012.545</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>357354359777.448</v>
+        <v>1103216264417.207</v>
       </c>
       <c r="K33" t="n">
-        <v>379</v>
+        <v>257</v>
       </c>
       <c r="L33" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
@@ -13637,37 +13406,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7.62</v>
+        <v>6.43</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="E34" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H34" t="n">
-        <v>19.3</v>
+        <v>11.2</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>118645.95</v>
+        <v>139330.545</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>397808593917.8433</v>
+        <v>1388019687752.122</v>
       </c>
       <c r="K34" t="n">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="L34" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
@@ -13675,37 +13444,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7.94</v>
+        <v>6.62</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H35" t="n">
-        <v>16.7</v>
+        <v>22.3</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>152199.95</v>
+        <v>474379.545</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>419262828058.2386</v>
+        <v>2983769049179.907</v>
       </c>
       <c r="K35" t="n">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="L35" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -13713,37 +13482,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>8.220000000000001</v>
+        <v>6.99</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.7</v>
+        <v>0.05</v>
       </c>
       <c r="E36" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F36" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H36" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>179836.95</v>
+        <v>381367.545</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>406717062198.634</v>
+        <v>4776793468529.646</v>
       </c>
       <c r="K36" t="n">
-        <v>422</v>
+        <v>312</v>
       </c>
       <c r="L36" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -13751,37 +13520,37 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>8.48</v>
+        <v>7.24</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.86</v>
+        <v>0.59</v>
       </c>
       <c r="E37" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H37" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>186706.95</v>
+        <v>350530.545</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>355445459130.5036</v>
+        <v>3555389125813.759</v>
       </c>
       <c r="K37" t="n">
-        <v>434</v>
+        <v>318</v>
       </c>
       <c r="L37" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
@@ -13789,37 +13558,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>8.67</v>
+        <v>7.41</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="E38" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F38" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H38" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>515692.95</v>
+        <v>1336419.545</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>1818946145804.807</v>
+        <v>9635687894928.84</v>
       </c>
       <c r="K38" t="n">
-        <v>461</v>
+        <v>353</v>
       </c>
       <c r="L38" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39">
@@ -13827,37 +13596,37 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>9.17</v>
+        <v>7.8</v>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="E39" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F39" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H39" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>285500.95</v>
+        <v>668358.5449999999</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>1896694722316.409</v>
+        <v>12471453273944.77</v>
       </c>
       <c r="K39" t="n">
-        <v>482</v>
+        <v>372</v>
       </c>
       <c r="L39" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
@@ -13865,37 +13634,37 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>9.460000000000001</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="E40" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F40" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H40" t="n">
-        <v>16.2</v>
+        <v>23.9</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>330480.95</v>
+        <v>2559409.545</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>1478443298828.012</v>
+        <v>24770578549247.41</v>
       </c>
       <c r="K40" t="n">
-        <v>492</v>
+        <v>406</v>
       </c>
       <c r="L40" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41">
@@ -13903,37 +13672,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>9.73</v>
+        <v>8.4</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="E41" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F41" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G41" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H41" t="n">
-        <v>29.6</v>
+        <v>10.8</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>963587.95</v>
+        <v>1159334.545</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>4493894359848.951</v>
+        <v>23899112958616.86</v>
       </c>
       <c r="K41" t="n">
-        <v>510</v>
+        <v>422</v>
       </c>
       <c r="L41" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42">
@@ -13941,37 +13710,37 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>10.22</v>
+        <v>8.58</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.03</v>
+        <v>0.95</v>
       </c>
       <c r="E42" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F42" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H42" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>677441.95</v>
+        <v>4030971.545</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>7066883248241.656</v>
+        <v>44170040672797.92</v>
       </c>
       <c r="K42" t="n">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="L42" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
@@ -13979,37 +13748,37 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>10.57</v>
+        <v>8.94</v>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F43" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H43" t="n">
-        <v>16.9</v>
+        <v>25.9</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>697334.95</v>
+        <v>6471117.545</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>5139872136634.361</v>
+        <v>82505364360709.38</v>
       </c>
       <c r="K43" t="n">
-        <v>546</v>
+        <v>490</v>
       </c>
       <c r="L43" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44">
@@ -14017,415 +13786,35 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>10.85</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="F44" t="n">
-        <v>69</v>
-      </c>
-      <c r="G44" t="n">
-        <v>70</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>12.3</v>
+        <v>24.9</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>602206.95</v>
+        <v>10340306.545</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>3173880616174.375</v>
+        <v>143926724709402.7</v>
       </c>
       <c r="K44" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L44" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="C45" t="n">
-        <v>12</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E45" t="n">
-        <v>65</v>
-      </c>
-      <c r="F45" t="n">
-        <v>69</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="n">
-        <v>12</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>813263.95</v>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>4127889095714.389</v>
-      </c>
-      <c r="K45" t="n">
-        <v>567</v>
-      </c>
-      <c r="L45" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="C46" t="n">
-        <v>12</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E46" t="n">
-        <v>65</v>
-      </c>
-      <c r="F46" t="n">
-        <v>79</v>
-      </c>
-      <c r="G46" t="n">
-        <v>80</v>
-      </c>
-      <c r="H46" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>2433449.95</v>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>13972679246120.67</v>
-      </c>
-      <c r="K46" t="n">
-        <v>581</v>
-      </c>
-      <c r="L46" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="C47" t="n">
-        <v>13</v>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E47" t="n">
-        <v>71</v>
-      </c>
-      <c r="F47" t="n">
-        <v>79</v>
-      </c>
-      <c r="G47" t="n">
-        <v>80</v>
-      </c>
-      <c r="H47" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>1434488.95</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>18583109537091.75</v>
-      </c>
-      <c r="K47" t="n">
-        <v>599</v>
-      </c>
-      <c r="L47" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="C48" t="n">
-        <v>13</v>
-      </c>
-      <c r="D48" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E48" t="n">
-        <v>71</v>
-      </c>
-      <c r="F48" t="n">
-        <v>79</v>
-      </c>
-      <c r="G48" t="n">
-        <v>80</v>
-      </c>
-      <c r="H48" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>1455591.95</v>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>13303539828062.83</v>
-      </c>
-      <c r="K48" t="n">
-        <v>637</v>
-      </c>
-      <c r="L48" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="C49" t="n">
-        <v>13</v>
-      </c>
-      <c r="D49" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E49" t="n">
-        <v>75</v>
-      </c>
-      <c r="F49" t="n">
-        <v>89</v>
-      </c>
-      <c r="G49" t="n">
-        <v>90</v>
-      </c>
-      <c r="H49" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>3822461.95</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>27375176585439.12</v>
-      </c>
-      <c r="K49" t="n">
-        <v>677</v>
-      </c>
-      <c r="L49" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="C50" t="n">
-        <v>14</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E50" t="n">
-        <v>81</v>
-      </c>
-      <c r="F50" t="n">
-        <v>89</v>
-      </c>
-      <c r="G50" t="n">
-        <v>90</v>
-      </c>
-      <c r="H50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>2295750.95</v>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>39954631647800.55</v>
-      </c>
-      <c r="K50" t="n">
-        <v>689</v>
-      </c>
-      <c r="L50" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="C51" t="n">
-        <v>14</v>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E51" t="n">
-        <v>81</v>
-      </c>
-      <c r="F51" t="n">
-        <v>99</v>
-      </c>
-      <c r="G51" t="n">
-        <v>100</v>
-      </c>
-      <c r="H51" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>6277400.95</v>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>63056381076818.23</v>
-      </c>
-      <c r="K51" t="n">
-        <v>718</v>
-      </c>
-      <c r="L51" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="C52" t="n">
-        <v>14</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>91</v>
-      </c>
-      <c r="F52" t="n">
-        <v>99</v>
-      </c>
-      <c r="G52" t="n">
-        <v>100</v>
-      </c>
-      <c r="H52" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>7422518.95</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>65113825222018.42</v>
-      </c>
-      <c r="K52" t="n">
-        <v>734</v>
-      </c>
-      <c r="L52" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="C53" t="n">
-        <v>15</v>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E53" t="n">
-        <v>91</v>
-      </c>
-      <c r="F53" t="n">
-        <v>99</v>
-      </c>
-      <c r="G53" t="n">
-        <v>100</v>
-      </c>
-      <c r="H53" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>3555446.95</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>64171269367218.61</v>
-      </c>
-      <c r="K53" t="n">
-        <v>767</v>
-      </c>
-      <c r="L53" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="C54" t="n">
-        <v>15</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E54" t="n">
-        <v>91</v>
-      </c>
-      <c r="F54" t="n">
-        <v>100</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I54" s="11" t="n">
-        <v>4253496.95</v>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>51044152246078.38</v>
-      </c>
-      <c r="K54" t="n">
-        <v>794</v>
-      </c>
-      <c r="L54" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/밸런스 시뮬레이터.xlsx
+++ b/Data_Table/밸런스 시뮬레이터.xlsx
@@ -906,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I23" t="n">
         <v>6</v>
@@ -938,10 +938,10 @@
         <v>12</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>65</v>
@@ -970,10 +970,10 @@
         <v>16</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>80</v>
@@ -1002,10 +1002,10 @@
         <v>20</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>96</v>
@@ -1034,10 +1034,10 @@
         <v>24</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1700</v>
+        <v>1680</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>102</v>
@@ -1066,10 +1066,10 @@
         <v>27</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>4070</v>
+        <v>3740</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>141</v>
@@ -1098,10 +1098,10 @@
         <v>30</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>17750</v>
+        <v>18470</v>
       </c>
       <c r="I29" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>155</v>
@@ -1130,10 +1130,10 @@
         <v>33</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>27000</v>
+        <v>48000</v>
       </c>
       <c r="I30" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>180</v>
@@ -1162,10 +1162,10 @@
         <v>36</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>45000</v>
+        <v>77000</v>
       </c>
       <c r="I31" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>210</v>
@@ -1194,10 +1194,10 @@
         <v>39</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>165000</v>
+        <v>788000</v>
       </c>
       <c r="I32" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>250</v>
@@ -1226,10 +1226,10 @@
         <v>42</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>378000</v>
+        <v>2595000</v>
       </c>
       <c r="I33" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>295</v>
@@ -1258,10 +1258,10 @@
         <v>45</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1076000</v>
+        <v>11128000</v>
       </c>
       <c r="I34" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>345</v>
@@ -1290,10 +1290,10 @@
         <v>48</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1613000</v>
+        <v>62100000</v>
       </c>
       <c r="I35" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>400</v>
@@ -1322,10 +1322,10 @@
         <v>51</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2416000</v>
+        <v>190080000</v>
       </c>
       <c r="I36" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>460</v>
@@ -1354,10 +1354,10 @@
         <v>54</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>4032000</v>
+        <v>583200000</v>
       </c>
       <c r="I37" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>525</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.97</v>
+        <v>7.36</v>
       </c>
       <c r="C4" t="n">
-        <v>9.779999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="5">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.65</v>
+        <v>16.35</v>
       </c>
       <c r="C7" t="n">
-        <v>13.65</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="8">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="C10" t="n">
-        <v>1.42</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.61</v>
+        <v>1.28</v>
       </c>
       <c r="C11" t="n">
-        <v>3.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="12">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.61</v>
+        <v>1.28</v>
       </c>
       <c r="C12" t="n">
-        <v>3.79</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="13">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.81</v>
+        <v>1.82</v>
       </c>
       <c r="C13" t="n">
-        <v>4.98</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.65</v>
+        <v>2.35</v>
       </c>
       <c r="C14" t="n">
-        <v>5.92</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="15">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.71</v>
+        <v>3.76</v>
       </c>
       <c r="C15" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.97</v>
+        <v>7.36</v>
       </c>
       <c r="C16" t="n">
-        <v>9.779999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="17">
@@ -1581,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1921,10 +1921,10 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="6" t="n">
-        <v>300</v>
+        <v>95.87</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>57.6</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>8</v>
@@ -2008,13 +2008,13 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="6" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>58.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -2095,13 +2095,13 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="6" t="n">
-        <v>661</v>
+        <v>192</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>58.7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13.21</v>
+        <v>16.01</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -2182,13 +2182,13 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="6" t="n">
-        <v>873</v>
+        <v>347</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>59.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>17.46</v>
+        <v>28.96</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1500</v>
+        <v>789</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>30</v>
+        <v>65.83</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>6</v>
@@ -2360,13 +2360,13 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="6" t="n">
-        <v>1360</v>
+        <v>440</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>60.3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>27.21</v>
+        <v>36.69</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
@@ -2447,13 +2447,13 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="6" t="n">
-        <v>1600</v>
+        <v>611</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>60.8</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>32.09</v>
+        <v>51.01</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -2534,13 +2534,13 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="6" t="n">
-        <v>1890</v>
+        <v>758</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>61.3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>37.84</v>
+        <v>63.23</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -2616,21 +2616,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="6" t="n">
-        <v>2900</v>
+        <v>1040</v>
       </c>
       <c r="E11" t="n">
-        <v>89.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>58</v>
+        <v>86.73</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" s="8">
         <f>IF($E11*'설정'!$C$5*IF(('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)&lt;1,('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$6),('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E11*'설정'!$C$5*IF(('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)&lt;1,('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$6),('설정'!$C$22*IF($A11&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D11)^(-'설정'!$C$7)),0))</f>
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>3010</v>
+        <v>1680</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>60.21</v>
+        <v>141</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H12" s="8">
         <f>IF($E12*'설정'!$C$5*IF(('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)&lt;1,('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$6),('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E12*'설정'!$C$5*IF(('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)&lt;1,('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$6),('설정'!$C$22*IF($A12&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D12)^(-'설정'!$C$7)),0))</f>
@@ -2794,21 +2794,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>3070</v>
+        <v>2110</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>61.44</v>
+        <v>176</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" s="8">
         <f>IF($E13*'설정'!$C$5*IF(('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)&lt;1,('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$6),('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E13*'설정'!$C$5*IF(('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)&lt;1,('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$6),('설정'!$C$22*IF($A13&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D13)^(-'설정'!$C$7)),0))</f>
@@ -2881,21 +2881,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>3610</v>
+        <v>834</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>63.5</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>72.09999999999999</v>
+        <v>69.62</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="8">
         <f>IF($E14*'설정'!$C$5*IF(('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)&lt;1,('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$6),('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E14*'설정'!$C$5*IF(('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)&lt;1,('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$6),('설정'!$C$22*IF($A14&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D14)^(-'설정'!$C$7)),0))</f>
@@ -2968,21 +2968,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="6" t="n">
-        <v>5500</v>
+        <v>1280</v>
       </c>
       <c r="E15" t="n">
-        <v>93.8</v>
+        <v>64</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H15" s="8">
         <f>IF($E15*'설정'!$C$5*IF(('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)&lt;1,('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$6),('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E15*'설정'!$C$5*IF(('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)&lt;1,('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$6),('설정'!$C$22*IF($A15&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D15)^(-'설정'!$C$7)),0))</f>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="6" t="n">
-        <v>4850</v>
+        <v>1430</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>64.5</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>97.02</v>
+        <v>119</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="8">
         <f>IF($E16*'설정'!$C$5*IF(('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)&lt;1,('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$6),('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E16*'설정'!$C$5*IF(('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)&lt;1,('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$6),('설정'!$C$22*IF($A16&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D16)^(-'설정'!$C$7)),0))</f>
@@ -3151,16 +3151,16 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>6400</v>
+        <v>2110</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>90</v>
+        <v>81.3</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" s="8">
         <f>IF($E17*'설정'!$C$5*IF(('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)&lt;1,('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$6),('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E17*'설정'!$C$5*IF(('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)&lt;1,('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$6),('설정'!$C$22*IF($A17&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D17)^(-'설정'!$C$7)),0))</f>
@@ -3238,16 +3238,16 @@
       </c>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="9" t="n">
-        <v>6380</v>
+        <v>2370</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>72</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="8">
         <f>IF($E18*'설정'!$C$5*IF(('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)&lt;1,('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$6),('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E18*'설정'!$C$5*IF(('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)&lt;1,('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$6),('설정'!$C$22*IF($A18&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D18)^(-'설정'!$C$7)),0))</f>
@@ -3320,21 +3320,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="6" t="n">
-        <v>7310</v>
+        <v>3120</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>93.8</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H19" s="8">
         <f>IF($E19*'설정'!$C$5*IF(('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)&lt;1,('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$6),('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E19*'설정'!$C$5*IF(('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)&lt;1,('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$6),('설정'!$C$22*IF($A19&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D19)^(-'설정'!$C$7)),0))</f>
@@ -3407,21 +3407,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" s="6" t="n">
-        <v>10900</v>
+        <v>1450</v>
       </c>
       <c r="E20" t="n">
-        <v>99.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="8">
         <f>IF($E20*'설정'!$C$5*IF(('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)&lt;1,('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$6),('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E20*'설정'!$C$5*IF(('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)&lt;1,('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$6),('설정'!$C$22*IF($A20&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D20)^(-'설정'!$C$7)),0))</f>
@@ -3494,21 +3494,21 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="9" t="n">
-        <v>9990</v>
+        <v>1890</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>72</v>
+        <v>67.2</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" s="8">
         <f>IF($E21*'설정'!$C$5*IF(('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)&lt;1,('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$6),('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E21*'설정'!$C$5*IF(('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)&lt;1,('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$6),('설정'!$C$22*IF($A21&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D21)^(-'설정'!$C$7)),0))</f>
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>13700</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="8">
         <f>IF($E22*'설정'!$C$5*IF(('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)&lt;1,('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$6),('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E22*'설정'!$C$5*IF(('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)&lt;1,('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$6),('설정'!$C$22*IF($A22&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D22)^(-'설정'!$C$7)),0))</f>
@@ -3677,16 +3677,16 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="6" t="n">
-        <v>14200</v>
+        <v>2790</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>68.3</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" s="8">
         <f>IF($E23*'설정'!$C$5*IF(('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)&lt;1,('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$6),('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E23*'설정'!$C$5*IF(('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)&lt;1,('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$6),('설정'!$C$22*IF($A23&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D23)^(-'설정'!$C$7)),0))</f>
@@ -3764,13 +3764,13 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" s="6" t="n">
-        <v>16900</v>
+        <v>3520</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>68.8</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="G24" t="n">
         <v>19</v>
@@ -3846,21 +3846,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="6" t="n">
-        <v>26200</v>
+        <v>3630</v>
       </c>
       <c r="E25" t="n">
-        <v>105</v>
+        <v>69.3</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>524</v>
+        <v>303</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H25" s="8">
         <f>IF($E25*'설정'!$C$5*IF(('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)&lt;1,('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$6),('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E25*'설정'!$C$5*IF(('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)&lt;1,('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$6),('설정'!$C$22*IF($A25&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D25)^(-'설정'!$C$7)),0))</f>
@@ -3933,21 +3933,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" s="6" t="n">
-        <v>23600</v>
+        <v>5100</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="8">
         <f>IF($E26*'설정'!$C$5*IF(('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)&lt;1,('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$6),('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E26*'설정'!$C$5*IF(('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)&lt;1,('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$6),('설정'!$C$22*IF($A26&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D26)^(-'설정'!$C$7)),0))</f>
@@ -4029,16 +4029,16 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>31800</v>
+        <v>3000</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>636</v>
+        <v>250</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27" s="8">
         <f>IF($E27*'설정'!$C$5*IF(('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)&lt;1,('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$6),('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E27*'설정'!$C$5*IF(('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)&lt;1,('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$6),('설정'!$C$22*IF($A27&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D27)^(-'설정'!$C$7)),0))</f>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" s="6" t="n">
-        <v>32400</v>
+        <v>3650</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>647</v>
+        <v>304</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H28" s="8">
         <f>IF($E28*'설정'!$C$5*IF(('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)&lt;1,('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$6),('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E28*'설정'!$C$5*IF(('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)&lt;1,('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$6),('설정'!$C$22*IF($A28&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D28)^(-'설정'!$C$7)),0))</f>
@@ -4203,16 +4203,16 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" s="6" t="n">
-        <v>37900</v>
+        <v>5000</v>
       </c>
       <c r="E29" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>758</v>
+        <v>417</v>
       </c>
       <c r="G29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H29" s="8">
         <f>IF($E29*'설정'!$C$5*IF(('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)&lt;1,('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$6),('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E29*'설정'!$C$5*IF(('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)&lt;1,('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$6),('설정'!$C$22*IF($A29&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D29)^(-'설정'!$C$7)),0))</f>
@@ -4285,21 +4285,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="6" t="n">
-        <v>57700</v>
+        <v>10400</v>
       </c>
       <c r="E30" t="n">
-        <v>110.6</v>
+        <v>72</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1150</v>
+        <v>868</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H30" s="8">
         <f>IF($E30*'설정'!$C$5*IF(('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)&lt;1,('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$6),('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E30*'설정'!$C$5*IF(('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)&lt;1,('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$6),('설정'!$C$22*IF($A30&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D30)^(-'설정'!$C$7)),0))</f>
@@ -4372,21 +4372,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" s="6" t="n">
-        <v>56700</v>
+        <v>14000</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1130</v>
+        <v>1170</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H31" s="8">
         <f>IF($E31*'설정'!$C$5*IF(('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)&lt;1,('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$6),('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E31*'설정'!$C$5*IF(('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)&lt;1,('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$6),('설정'!$C$22*IF($A31&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D31)^(-'설정'!$C$7)),0))</f>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -4468,16 +4468,16 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>83400</v>
+        <v>19500</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1670</v>
+        <v>1630</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H32" s="8">
         <f>IF($E32*'설정'!$C$5*IF(('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)&lt;1,('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$6),('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E32*'설정'!$C$5*IF(('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)&lt;1,('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$6),('설정'!$C$22*IF($A32&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D32)^(-'설정'!$C$7)),0))</f>
@@ -4550,21 +4550,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="6" t="n">
-        <v>92700</v>
+        <v>12500</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1850</v>
+        <v>1040</v>
       </c>
       <c r="G33" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H33" s="8">
         <f>IF($E33*'설정'!$C$5*IF(('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)&lt;1,('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$6),('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E33*'설정'!$C$5*IF(('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)&lt;1,('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$6),('설정'!$C$22*IF($A33&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D33)^(-'설정'!$C$7)),0))</f>
@@ -4642,16 +4642,16 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="6" t="n">
-        <v>119000</v>
+        <v>17000</v>
       </c>
       <c r="E34" t="n">
-        <v>72</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2370</v>
+        <v>1420</v>
       </c>
       <c r="G34" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H34" s="8">
         <f>IF($E34*'설정'!$C$5*IF(('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)&lt;1,('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$6),('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E34*'설정'!$C$5*IF(('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)&lt;1,('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$6),('설정'!$C$22*IF($A34&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D34)^(-'설정'!$C$7)),0))</f>
@@ -4729,16 +4729,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="6" t="n">
-        <v>151000</v>
+        <v>22900</v>
       </c>
       <c r="E35" t="n">
-        <v>72</v>
+        <v>74.7</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>3030</v>
+        <v>1910</v>
       </c>
       <c r="G35" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H35" s="8">
         <f>IF($E35*'설정'!$C$5*IF(('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)&lt;1,('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$6),('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E35*'설정'!$C$5*IF(('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)&lt;1,('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$6),('설정'!$C$22*IF($A35&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D35)^(-'설정'!$C$7)),0))</f>
@@ -4811,21 +4811,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="6" t="n">
-        <v>252000</v>
+        <v>30500</v>
       </c>
       <c r="E36" t="n">
-        <v>117.6</v>
+        <v>75.2</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>5030</v>
+        <v>2540</v>
       </c>
       <c r="G36" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H36" s="8">
         <f>IF($E36*'설정'!$C$5*IF(('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)&lt;1,('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$6),('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E36*'설정'!$C$5*IF(('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)&lt;1,('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$6),('설정'!$C$22*IF($A36&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D36)^(-'설정'!$C$7)),0))</f>
@@ -4907,16 +4907,16 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>247000</v>
+        <v>46000</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>94.7</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>4930</v>
+        <v>3840</v>
       </c>
       <c r="G37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H37" s="8">
         <f>IF($E37*'설정'!$C$5*IF(('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)&lt;1,('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$6),('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E37*'설정'!$C$5*IF(('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)&lt;1,('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$6),('설정'!$C$22*IF($A37&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D37)^(-'설정'!$C$7)),0))</f>
@@ -4989,21 +4989,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="6" t="n">
-        <v>237000</v>
+        <v>60600</v>
       </c>
       <c r="E38" t="n">
-        <v>72</v>
+        <v>110.6</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>4750</v>
+        <v>5060</v>
       </c>
       <c r="G38" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H38" s="8">
         <f>IF($E38*'설정'!$C$5*IF(('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)&lt;1,('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$6),('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E38*'설정'!$C$5*IF(('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)&lt;1,('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$6),('설정'!$C$22*IF($A38&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D38)^(-'설정'!$C$7)),0))</f>
@@ -5076,21 +5076,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="6" t="n">
-        <v>263000</v>
+        <v>27600</v>
       </c>
       <c r="E39" t="n">
-        <v>72</v>
+        <v>76.8</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>5260</v>
+        <v>2310</v>
       </c>
       <c r="G39" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H39" s="8">
         <f>IF($E39*'설정'!$C$5*IF(('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)&lt;1,('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$6),('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E39*'설정'!$C$5*IF(('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)&lt;1,('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$6),('설정'!$C$22*IF($A39&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D39)^(-'설정'!$C$7)),0))</f>
@@ -5168,16 +5168,16 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" s="6" t="n">
-        <v>291000</v>
+        <v>40000</v>
       </c>
       <c r="E40" t="n">
-        <v>72</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>5820</v>
+        <v>3340</v>
       </c>
       <c r="G40" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H40" s="8">
         <f>IF($E40*'설정'!$C$5*IF(('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)&lt;1,('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$6),('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E40*'설정'!$C$5*IF(('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)&lt;1,('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$6),('설정'!$C$22*IF($A40&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D40)^(-'설정'!$C$7)),0))</f>
@@ -5255,16 +5255,16 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" s="6" t="n">
-        <v>322000</v>
+        <v>57200</v>
       </c>
       <c r="E41" t="n">
-        <v>72</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>6450</v>
+        <v>4770</v>
       </c>
       <c r="G41" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H41" s="8">
         <f>IF($E41*'설정'!$C$5*IF(('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)&lt;1,('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$6),('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E41*'설정'!$C$5*IF(('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)&lt;1,('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$6),('설정'!$C$22*IF($A41&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D41)^(-'설정'!$C$7)),0))</f>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -5346,16 +5346,16 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>464000</v>
+        <v>92300</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>9280</v>
+        <v>7710</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H42" s="8">
         <f>IF($E42*'설정'!$C$5*IF(('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)&lt;1,('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)^(-'설정'!$C$6),('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E42*'설정'!$C$5*IF(('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)&lt;1,('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)^(-'설정'!$C$6),('설정'!$C$22*IF($A42&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D42)^(-'설정'!$C$7)),0))</f>
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" s="6" t="n">
-        <v>378000</v>
+        <v>114000</v>
       </c>
       <c r="E43" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>7550</v>
+        <v>9480</v>
       </c>
       <c r="G43" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H43" s="8">
         <f>IF($E43*'설정'!$C$5*IF(('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)&lt;1,('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)^(-'설정'!$C$6),('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E43*'설정'!$C$5*IF(('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)&lt;1,('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)^(-'설정'!$C$6),('설정'!$C$22*IF($A43&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D43)^(-'설정'!$C$7)),0))</f>
@@ -5520,16 +5520,16 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" s="6" t="n">
-        <v>399000</v>
+        <v>146000</v>
       </c>
       <c r="E44" t="n">
-        <v>72</v>
+        <v>79.5</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>7990</v>
+        <v>12200</v>
       </c>
       <c r="G44" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H44" s="8">
         <f>IF($E44*'설정'!$C$5*IF(('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)&lt;1,('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)^(-'설정'!$C$6),('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E44*'설정'!$C$5*IF(('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)&lt;1,('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)^(-'설정'!$C$6),('설정'!$C$22*IF($A44&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D44)^(-'설정'!$C$7)),0))</f>
@@ -5602,21 +5602,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" s="6" t="n">
-        <v>422000</v>
+        <v>238000</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>117.6</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>8450</v>
+        <v>19800</v>
       </c>
       <c r="G45" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H45" s="8">
         <f>IF($E45*'설정'!$C$5*IF(('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)&lt;1,('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)^(-'설정'!$C$6),('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E45*'설정'!$C$5*IF(('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)&lt;1,('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)^(-'설정'!$C$6),('설정'!$C$22*IF($A45&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D45)^(-'설정'!$C$7)),0))</f>
@@ -5689,21 +5689,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" s="6" t="n">
-        <v>447000</v>
+        <v>137000</v>
       </c>
       <c r="E46" t="n">
-        <v>72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>8930</v>
+        <v>11400</v>
       </c>
       <c r="G46" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H46" s="8">
         <f>IF($E46*'설정'!$C$5*IF(('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)&lt;1,('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)^(-'설정'!$C$6),('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E46*'설정'!$C$5*IF(('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)&lt;1,('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)^(-'설정'!$C$6),('설정'!$C$22*IF($A46&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D46)^(-'설정'!$C$7)),0))</f>
@@ -5785,16 +5785,16 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>543000</v>
+        <v>205000</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>101.4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>10900</v>
+        <v>17100</v>
       </c>
       <c r="G47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H47" s="8">
         <f>IF($E47*'설정'!$C$5*IF(('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)&lt;1,('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$6),('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E47*'설정'!$C$5*IF(('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)&lt;1,('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$6),('설정'!$C$22*IF($A47&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D47)^(-'설정'!$C$7)),0))</f>
@@ -5867,21 +5867,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" s="6" t="n">
-        <v>650000</v>
+        <v>234000</v>
       </c>
       <c r="E48" t="n">
-        <v>126</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="G48" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H48" s="8">
         <f>IF($E48*'설정'!$C$5*IF(('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)&lt;1,('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$6),('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E48*'설정'!$C$5*IF(('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)&lt;1,('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$6),('설정'!$C$22*IF($A48&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D48)^(-'설정'!$C$7)),0))</f>
@@ -5954,21 +5954,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" s="6" t="n">
-        <v>630000</v>
+        <v>300000</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>82.2</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12600</v>
+        <v>25100</v>
       </c>
       <c r="G49" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H49" s="8">
         <f>IF($E49*'설정'!$C$5*IF(('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)&lt;1,('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$6),('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E49*'설정'!$C$5*IF(('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)&lt;1,('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$6),('설정'!$C$22*IF($A49&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D49)^(-'설정'!$C$7)),0))</f>
@@ -6046,16 +6046,16 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" s="6" t="n">
-        <v>794000</v>
+        <v>383000</v>
       </c>
       <c r="E50" t="n">
-        <v>72</v>
+        <v>82.7</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>15900</v>
+        <v>32000</v>
       </c>
       <c r="G50" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H50" s="8">
         <f>IF($E50*'설정'!$C$5*IF(('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)&lt;1,('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$6),('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E50*'설정'!$C$5*IF(('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)&lt;1,('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$6),('설정'!$C$22*IF($A50&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D50)^(-'설정'!$C$7)),0))</f>
@@ -6128,21 +6128,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" s="6" t="n">
-        <v>1000000</v>
+        <v>578000</v>
       </c>
       <c r="E51" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>20000</v>
+        <v>48200</v>
       </c>
       <c r="G51" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H51" s="8">
         <f>IF($E51*'설정'!$C$5*IF(('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)&lt;1,('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$6),('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E51*'설정'!$C$5*IF(('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)&lt;1,('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$6),('설정'!$C$22*IF($A51&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D51)^(-'설정'!$C$7)),0))</f>
@@ -6224,16 +6224,16 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1450000</v>
+        <v>359000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>90</v>
+        <v>104.7</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>29000</v>
+        <v>29900</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H52" s="8">
         <f>IF($E52*'설정'!$C$5*IF(('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)&lt;1,('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$6),('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E52*'설정'!$C$5*IF(('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)&lt;1,('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$6),('설정'!$C$22*IF($A52&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D52)^(-'설정'!$C$7)),0))</f>
@@ -6311,16 +6311,16 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" s="6" t="n">
-        <v>1590000</v>
+        <v>386000</v>
       </c>
       <c r="E53" t="n">
-        <v>72</v>
+        <v>84.3</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>31800</v>
+        <v>32200</v>
       </c>
       <c r="G53" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H53" s="8">
         <f>IF($E53*'설정'!$C$5*IF(('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)&lt;1,('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$6),('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E53*'설정'!$C$5*IF(('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)&lt;1,('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$6),('설정'!$C$22*IF($A53&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D53)^(-'설정'!$C$7)),0))</f>
@@ -6393,21 +6393,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" s="6" t="n">
-        <v>2600000</v>
+        <v>467000</v>
       </c>
       <c r="E54" t="n">
-        <v>126</v>
+        <v>84.8</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>52100</v>
+        <v>39000</v>
       </c>
       <c r="G54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H54" s="8">
         <f>IF($E54*'설정'!$C$5*IF(('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)&lt;1,('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$6),('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E54*'설정'!$C$5*IF(('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)&lt;1,('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$6),('설정'!$C$22*IF($A54&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D54)^(-'설정'!$C$7)),0))</f>
@@ -6480,21 +6480,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" s="6" t="n">
-        <v>2290000</v>
+        <v>561000</v>
       </c>
       <c r="E55" t="n">
-        <v>72</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>45800</v>
+        <v>46800</v>
       </c>
       <c r="G55" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H55" s="8">
         <f>IF($E55*'설정'!$C$5*IF(('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)&lt;1,('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$6),('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E55*'설정'!$C$5*IF(('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)&lt;1,('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$6),('설정'!$C$22*IF($A55&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D55)^(-'설정'!$C$7)),0))</f>
@@ -6572,16 +6572,16 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" s="6" t="n">
-        <v>2610000</v>
+        <v>668000</v>
       </c>
       <c r="E56" t="n">
-        <v>72</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>52300</v>
+        <v>55700</v>
       </c>
       <c r="G56" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H56" s="8">
         <f>IF($E56*'설정'!$C$5*IF(('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)&lt;1,('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$6),('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E56*'설정'!$C$5*IF(('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)&lt;1,('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$6),('설정'!$C$22*IF($A56&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D56)^(-'설정'!$C$7)),0))</f>
@@ -6663,16 +6663,16 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3440000</v>
+        <v>832000</v>
       </c>
       <c r="E57" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>68700</v>
+        <v>69400</v>
       </c>
       <c r="G57" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H57" s="8">
         <f>IF($E57*'설정'!$C$5*IF(('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)&lt;1,('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$6),('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E57*'설정'!$C$5*IF(('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)&lt;1,('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$6),('설정'!$C$22*IF($A57&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D57)^(-'설정'!$C$7)),0))</f>
@@ -6745,21 +6745,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" s="6" t="n">
-        <v>3410000</v>
+        <v>1020000</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>68300</v>
+        <v>84900</v>
       </c>
       <c r="G58" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H58" s="8">
         <f>IF($E58*'설정'!$C$5*IF(('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)&lt;1,('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$6),('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E58*'설정'!$C$5*IF(('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)&lt;1,('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$6),('설정'!$C$22*IF($A58&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D58)^(-'설정'!$C$7)),0))</f>
@@ -6832,21 +6832,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" s="6" t="n">
-        <v>3900000</v>
+        <v>567000</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>87.5</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>78000</v>
+        <v>47300</v>
       </c>
       <c r="G59" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H59" s="8">
         <f>IF($E59*'설정'!$C$5*IF(('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)&lt;1,('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$6),('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E59*'설정'!$C$5*IF(('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)&lt;1,('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$6),('설정'!$C$22*IF($A59&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D59)^(-'설정'!$C$7)),0))</f>
@@ -6919,21 +6919,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" s="6" t="n">
-        <v>5790000</v>
+        <v>820000</v>
       </c>
       <c r="E60" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>116000</v>
+        <v>68400</v>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H60" s="8">
         <f>IF($E60*'설정'!$C$5*IF(('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)&lt;1,('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$6),('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E60*'설정'!$C$5*IF(('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)&lt;1,('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$6),('설정'!$C$22*IF($A60&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D60)^(-'설정'!$C$7)),0))</f>
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" s="6" t="n">
-        <v>5240000</v>
+        <v>1170000</v>
       </c>
       <c r="E61" t="n">
-        <v>72</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>105000</v>
+        <v>97600</v>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H61" s="8">
         <f>IF($E61*'설정'!$C$5*IF(('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)&lt;1,('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$6),('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E61*'설정'!$C$5*IF(('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)&lt;1,('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$6),('설정'!$C$22*IF($A61&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D61)^(-'설정'!$C$7)),0))</f>
@@ -7102,16 +7102,16 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>7080000</v>
+        <v>1890000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>90</v>
+        <v>111.4</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>142000</v>
+        <v>157000</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H62" s="8">
         <f>IF($E62*'설정'!$C$5*IF(('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)&lt;1,('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$6),('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E62*'설정'!$C$5*IF(('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)&lt;1,('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$6),('설정'!$C$22*IF($A62&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D62)^(-'설정'!$C$7)),0))</f>
@@ -7189,16 +7189,16 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" s="6" t="n">
-        <v>7240000</v>
+        <v>2320000</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>145000</v>
+        <v>194000</v>
       </c>
       <c r="G63" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H63" s="8">
         <f>IF($E63*'설정'!$C$5*IF(('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)&lt;1,('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$6),('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E63*'설정'!$C$5*IF(('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)&lt;1,('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$6),('설정'!$C$22*IF($A63&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D63)^(-'설정'!$C$7)),0))</f>
@@ -7276,13 +7276,13 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" s="6" t="n">
-        <v>8520000</v>
+        <v>2980000</v>
       </c>
       <c r="E64" t="n">
-        <v>72</v>
+        <v>90.2</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>170000</v>
+        <v>249000</v>
       </c>
       <c r="G64" t="n">
         <v>59</v>
@@ -7358,21 +7358,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" s="6" t="n">
-        <v>10000000</v>
+        <v>4870000</v>
       </c>
       <c r="E65" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>200000</v>
+        <v>407000</v>
       </c>
       <c r="G65" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H65" s="8">
         <f>IF($E65*'설정'!$C$5*IF(('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)&lt;1,('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$6),('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E65*'설정'!$C$5*IF(('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)&lt;1,('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$6),('설정'!$C$22*IF($A65&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D65)^(-'설정'!$C$7)),0))</f>
@@ -7445,21 +7445,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" s="6" t="n">
-        <v>15300000</v>
+        <v>2730000</v>
       </c>
       <c r="E66" t="n">
-        <v>126</v>
+        <v>91.2</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>306000</v>
+        <v>228000</v>
       </c>
       <c r="G66" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H66" s="8">
         <f>IF($E66*'설정'!$C$5*IF(('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)&lt;1,('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$6),('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E66*'설정'!$C$5*IF(('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)&lt;1,('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$6),('설정'!$C$22*IF($A66&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D66)^(-'설정'!$C$7)),0))</f>
@@ -7541,16 +7541,16 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>14900000</v>
+        <v>4250000</v>
       </c>
       <c r="E67" t="n">
-        <v>90</v>
+        <v>114.7</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>299000</v>
+        <v>355000</v>
       </c>
       <c r="G67" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H67" s="8">
         <f>IF($E67*'설정'!$C$5*IF(('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)&lt;1,('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$6),('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E67*'설정'!$C$5*IF(('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)&lt;1,('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$6),('설정'!$C$22*IF($A67&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D67)^(-'설정'!$C$7)),0))</f>
@@ -7628,16 +7628,16 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" s="6" t="n">
-        <v>14300000</v>
+        <v>5020000</v>
       </c>
       <c r="E68" t="n">
-        <v>72</v>
+        <v>92.3</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>286000</v>
+        <v>419000</v>
       </c>
       <c r="G68" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H68" s="8">
         <f>IF($E68*'설정'!$C$5*IF(('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)&lt;1,('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$6),('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E68*'설정'!$C$5*IF(('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)&lt;1,('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$6),('설정'!$C$22*IF($A68&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D68)^(-'설정'!$C$7)),0))</f>
@@ -7715,16 +7715,16 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" s="6" t="n">
-        <v>15800000</v>
+        <v>6710000</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>92.8</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>315000</v>
+        <v>560000</v>
       </c>
       <c r="G69" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H69" s="8">
         <f>IF($E69*'설정'!$C$5*IF(('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)&lt;1,('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$6),('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E69*'설정'!$C$5*IF(('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)&lt;1,('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$6),('설정'!$C$22*IF($A69&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D69)^(-'설정'!$C$7)),0))</f>
@@ -7802,13 +7802,13 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" s="6" t="n">
-        <v>17400000</v>
+        <v>8870000</v>
       </c>
       <c r="E70" t="n">
-        <v>72</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>348000</v>
+        <v>740000</v>
       </c>
       <c r="G70" t="n">
         <v>65</v>
@@ -7884,21 +7884,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" s="6" t="n">
-        <v>19200000</v>
+        <v>13600000</v>
       </c>
       <c r="E71" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>383000</v>
+        <v>1130000</v>
       </c>
       <c r="G71" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H71" s="8">
         <f>IF($E71*'설정'!$C$5*IF(('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)&lt;1,('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$6),('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E71*'설정'!$C$5*IF(('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)&lt;1,('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$6),('설정'!$C$22*IF($A71&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D71)^(-'설정'!$C$7)),0))</f>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -7980,16 +7980,16 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>27500000</v>
+        <v>9000000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>157.5</v>
+        <v>118</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>549000</v>
+        <v>751000</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H72" s="8">
         <f>IF($E72*'설정'!$C$5*IF(('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)&lt;1,('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)^(-'설정'!$C$6),('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E72*'설정'!$C$5*IF(('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)&lt;1,('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)^(-'설정'!$C$6),('설정'!$C$22*IF($A72&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D72)^(-'설정'!$C$7)),0))</f>
@@ -8062,21 +8062,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" s="6" t="n">
-        <v>22400000</v>
+        <v>11000000</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>448000</v>
+        <v>918000</v>
       </c>
       <c r="G73" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H73" s="8">
         <f>IF($E73*'설정'!$C$5*IF(('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)&lt;1,('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)^(-'설정'!$C$6),('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E73*'설정'!$C$5*IF(('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)&lt;1,('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)^(-'설정'!$C$6),('설정'!$C$22*IF($A73&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D73)^(-'설정'!$C$7)),0))</f>
@@ -8154,16 +8154,16 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" s="6" t="n">
-        <v>23700000</v>
+        <v>15200000</v>
       </c>
       <c r="E74" t="n">
-        <v>72</v>
+        <v>95.5</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>475000</v>
+        <v>1260000</v>
       </c>
       <c r="G74" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H74" s="8">
         <f>IF($E74*'설정'!$C$5*IF(('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)&lt;1,('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)^(-'설정'!$C$6),('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E74*'설정'!$C$5*IF(('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)&lt;1,('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)^(-'설정'!$C$6),('설정'!$C$22*IF($A74&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D74)^(-'설정'!$C$7)),0))</f>
@@ -8241,16 +8241,16 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" s="6" t="n">
-        <v>25200000</v>
+        <v>20700000</v>
       </c>
       <c r="E75" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>503000</v>
+        <v>1730000</v>
       </c>
       <c r="G75" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H75" s="8">
         <f>IF($E75*'설정'!$C$5*IF(('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)&lt;1,('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)^(-'설정'!$C$6),('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E75*'설정'!$C$5*IF(('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)&lt;1,('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)^(-'설정'!$C$6),('설정'!$C$22*IF($A75&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D75)^(-'설정'!$C$7)),0))</f>
@@ -8328,16 +8328,16 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" s="6" t="n">
-        <v>26700000</v>
+        <v>28000000</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>534000</v>
+        <v>2330000</v>
       </c>
       <c r="G76" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H76" s="8">
         <f>IF($E76*'설정'!$C$5*IF(('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)&lt;1,('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)^(-'설정'!$C$6),('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E76*'설정'!$C$5*IF(('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)&lt;1,('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)^(-'설정'!$C$6),('설정'!$C$22*IF($A76&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D76)^(-'설정'!$C$7)),0))</f>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8419,16 +8419,16 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>32500000</v>
+        <v>45000000</v>
       </c>
       <c r="E77" t="n">
-        <v>90</v>
+        <v>155.4</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650000</v>
+        <v>3760000</v>
       </c>
       <c r="G77" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H77" s="8">
         <f>IF($E77*'설정'!$C$5*IF(('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)&lt;1,('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$6),('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E77*'설정'!$C$5*IF(('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)&lt;1,('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$6),('설정'!$C$22*IF($A77&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D77)^(-'설정'!$C$7)),0))</f>
@@ -8501,21 +8501,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" s="6" t="n">
-        <v>30000000</v>
+        <v>38600000</v>
       </c>
       <c r="E78" t="n">
-        <v>72</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>600000</v>
+        <v>3220000</v>
       </c>
       <c r="G78" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H78" s="8">
         <f>IF($E78*'설정'!$C$5*IF(('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)&lt;1,('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$6),('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E78*'설정'!$C$5*IF(('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)&lt;1,('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$6),('설정'!$C$22*IF($A78&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D78)^(-'설정'!$C$7)),0))</f>
@@ -8588,21 +8588,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" s="6" t="n">
-        <v>41300000</v>
+        <v>52100000</v>
       </c>
       <c r="E79" t="n">
-        <v>126</v>
+        <v>98.2</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>826000</v>
+        <v>4350000</v>
       </c>
       <c r="G79" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H79" s="8">
         <f>IF($E79*'설정'!$C$5*IF(('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)&lt;1,('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$6),('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E79*'설정'!$C$5*IF(('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)&lt;1,('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$6),('설정'!$C$22*IF($A79&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D79)^(-'설정'!$C$7)),0))</f>
@@ -8675,21 +8675,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" s="6" t="n">
-        <v>33600000</v>
+        <v>69600000</v>
       </c>
       <c r="E80" t="n">
-        <v>72</v>
+        <v>98.7</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>671000</v>
+        <v>5810000</v>
       </c>
       <c r="G80" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H80" s="8">
         <f>IF($E80*'설정'!$C$5*IF(('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)&lt;1,('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$6),('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E80*'설정'!$C$5*IF(('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)&lt;1,('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$6),('설정'!$C$22*IF($A80&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D80)^(-'설정'!$C$7)),0))</f>
@@ -8767,16 +8767,16 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" s="6" t="n">
-        <v>35400000</v>
+        <v>91900000</v>
       </c>
       <c r="E81" t="n">
-        <v>72</v>
+        <v>99.2</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>709000</v>
+        <v>7670000</v>
       </c>
       <c r="G81" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H81" s="8">
         <f>IF($E81*'설정'!$C$5*IF(('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)&lt;1,('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$6),('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E81*'설정'!$C$5*IF(('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)&lt;1,('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$6),('설정'!$C$22*IF($A81&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D81)^(-'설정'!$C$7)),0))</f>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8858,16 +8858,16 @@
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>43000000</v>
+        <v>144000000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>90</v>
+        <v>157.5</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>861000</v>
+        <v>12100000</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H82" s="8">
         <f>IF($E82*'설정'!$C$5*IF(('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)&lt;1,('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$6),('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E82*'설정'!$C$5*IF(('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)&lt;1,('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$6),('설정'!$C$22*IF($A82&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D82)^(-'설정'!$C$7)),0))</f>
@@ -8940,21 +8940,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" s="6" t="n">
-        <v>39500000</v>
+        <v>138000000</v>
       </c>
       <c r="E83" t="n">
-        <v>72</v>
+        <v>100.3</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>790000</v>
+        <v>11500000</v>
       </c>
       <c r="G83" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H83" s="8">
         <f>IF($E83*'설정'!$C$5*IF(('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)&lt;1,('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$6),('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E83*'설정'!$C$5*IF(('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)&lt;1,('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$6),('설정'!$C$22*IF($A83&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D83)^(-'설정'!$C$7)),0))</f>
@@ -9032,16 +9032,16 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" s="6" t="n">
-        <v>41700000</v>
+        <v>178000000</v>
       </c>
       <c r="E84" t="n">
-        <v>72</v>
+        <v>100.8</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>834000</v>
+        <v>14800000</v>
       </c>
       <c r="G84" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H84" s="8">
         <f>IF($E84*'설정'!$C$5*IF(('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)&lt;1,('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$6),('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E84*'설정'!$C$5*IF(('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)&lt;1,('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$6),('설정'!$C$22*IF($A84&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D84)^(-'설정'!$C$7)),0))</f>
@@ -9119,16 +9119,16 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" s="6" t="n">
-        <v>44000000</v>
+        <v>227000000</v>
       </c>
       <c r="E85" t="n">
-        <v>72</v>
+        <v>101.4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>881000</v>
+        <v>19000000</v>
       </c>
       <c r="G85" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H85" s="8">
         <f>IF($E85*'설정'!$C$5*IF(('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)&lt;1,('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$6),('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E85*'설정'!$C$5*IF(('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)&lt;1,('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$6),('설정'!$C$22*IF($A85&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D85)^(-'설정'!$C$7)),0))</f>
@@ -9201,21 +9201,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" s="6" t="n">
-        <v>60500000</v>
+        <v>287000000</v>
       </c>
       <c r="E86" t="n">
-        <v>126</v>
+        <v>101.9</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1210000</v>
+        <v>24000000</v>
       </c>
       <c r="G86" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H86" s="8">
         <f>IF($E86*'설정'!$C$5*IF(('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)&lt;1,('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$6),('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E86*'설정'!$C$5*IF(('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)&lt;1,('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$6),('설정'!$C$22*IF($A86&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D86)^(-'설정'!$C$7)),0))</f>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9297,16 +9297,16 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>56200000</v>
+        <v>433000000</v>
       </c>
       <c r="E87" t="n">
-        <v>90</v>
+        <v>159.6</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1120000</v>
+        <v>36100000</v>
       </c>
       <c r="G87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H87" s="8">
         <f>IF($E87*'설정'!$C$5*IF(('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)&lt;1,('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$6),('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E87*'설정'!$C$5*IF(('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)&lt;1,('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$6),('설정'!$C$22*IF($A87&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D87)^(-'설정'!$C$7)),0))</f>
@@ -9379,21 +9379,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" s="6" t="n">
-        <v>51300000</v>
+        <v>422000000</v>
       </c>
       <c r="E88" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>1030000</v>
+        <v>35200000</v>
       </c>
       <c r="G88" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H88" s="8">
         <f>IF($E88*'설정'!$C$5*IF(('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)&lt;1,('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$6),('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E88*'설정'!$C$5*IF(('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)&lt;1,('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$6),('설정'!$C$22*IF($A88&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D88)^(-'설정'!$C$7)),0))</f>
@@ -9471,16 +9471,16 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" s="6" t="n">
-        <v>53900000</v>
+        <v>542000000</v>
       </c>
       <c r="E89" t="n">
-        <v>72</v>
+        <v>103.5</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1080000</v>
+        <v>45200000</v>
       </c>
       <c r="G89" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H89" s="8">
         <f>IF($E89*'설정'!$C$5*IF(('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)&lt;1,('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$6),('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E89*'설정'!$C$5*IF(('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)&lt;1,('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$6),('설정'!$C$22*IF($A89&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D89)^(-'설정'!$C$7)),0))</f>
@@ -9558,16 +9558,16 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" s="6" t="n">
-        <v>56600000</v>
+        <v>688000000</v>
       </c>
       <c r="E90" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1130000</v>
+        <v>57400000</v>
       </c>
       <c r="G90" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H90" s="8">
         <f>IF($E90*'설정'!$C$5*IF(('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)&lt;1,('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$6),('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E90*'설정'!$C$5*IF(('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)&lt;1,('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$6),('설정'!$C$22*IF($A90&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D90)^(-'설정'!$C$7)),0))</f>
@@ -9645,13 +9645,13 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" s="6" t="n">
-        <v>59500000</v>
+        <v>863000000</v>
       </c>
       <c r="E91" t="n">
-        <v>72</v>
+        <v>104.6</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1190000</v>
+        <v>72000000</v>
       </c>
       <c r="G91" t="n">
         <v>86</v>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9736,16 +9736,16 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>71800000</v>
+        <v>1290000000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>90</v>
+        <v>161.7</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>1440000</v>
+        <v>108000000</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H92" s="8">
         <f>IF($E92*'설정'!$C$5*IF(('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)&lt;1,('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$6),('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E92*'설정'!$C$5*IF(('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)&lt;1,('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$6),('설정'!$C$22*IF($A92&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D92)^(-'설정'!$C$7)),0))</f>
@@ -9818,21 +9818,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" s="6" t="n">
-        <v>65600000</v>
+        <v>1290000000</v>
       </c>
       <c r="E93" t="n">
-        <v>72</v>
+        <v>105.6</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1310000</v>
+        <v>108000000</v>
       </c>
       <c r="G93" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H93" s="8">
         <f>IF($E93*'설정'!$C$5*IF(('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)&lt;1,('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$6),('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E93*'설정'!$C$5*IF(('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)&lt;1,('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$6),('설정'!$C$22*IF($A93&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D93)^(-'설정'!$C$7)),0))</f>
@@ -9905,21 +9905,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>허들</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" s="6" t="n">
-        <v>89600000</v>
+        <v>1550000000</v>
       </c>
       <c r="E94" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1790000</v>
+        <v>129000000</v>
       </c>
       <c r="G94" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H94" s="8">
         <f>IF($E94*'설정'!$C$5*IF(('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)&lt;1,('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$6),('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E94*'설정'!$C$5*IF(('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)&lt;1,('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$6),('설정'!$C$22*IF($A94&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D94)^(-'설정'!$C$7)),0))</f>
@@ -9992,21 +9992,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" s="6" t="n">
-        <v>71000000</v>
+        <v>1830000000</v>
       </c>
       <c r="E95" t="n">
-        <v>72</v>
+        <v>106.7</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>1420000</v>
+        <v>153000000</v>
       </c>
       <c r="G95" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H95" s="8">
         <f>IF($E95*'설정'!$C$5*IF(('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)&lt;1,('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$6),('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E95*'설정'!$C$5*IF(('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)&lt;1,('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$6),('설정'!$C$22*IF($A95&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D95)^(-'설정'!$C$7)),0))</f>
@@ -10088,16 +10088,16 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>84100000</v>
+        <v>2450000000</v>
       </c>
       <c r="E96" t="n">
-        <v>90</v>
+        <v>134.1</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>1680000</v>
+        <v>204000000</v>
       </c>
       <c r="G96" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H96" s="8">
         <f>IF($E96*'설정'!$C$5*IF(('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)&lt;1,('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$6),('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E96*'설정'!$C$5*IF(('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)&lt;1,('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$6),('설정'!$C$22*IF($A96&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D96)^(-'설정'!$C$7)),0))</f>
@@ -10175,16 +10175,16 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" s="6" t="n">
-        <v>75300000</v>
+        <v>2500000000</v>
       </c>
       <c r="E97" t="n">
-        <v>72</v>
+        <v>107.8</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1510000</v>
+        <v>208000000</v>
       </c>
       <c r="G97" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H97" s="8">
         <f>IF($E97*'설정'!$C$5*IF(('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)&lt;1,('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$6),('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E97*'설정'!$C$5*IF(('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)&lt;1,('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$6),('설정'!$C$22*IF($A97&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D97)^(-'설정'!$C$7)),0))</f>
@@ -10262,16 +10262,16 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" s="6" t="n">
-        <v>77600000</v>
+        <v>2880000000</v>
       </c>
       <c r="E98" t="n">
-        <v>72</v>
+        <v>108.3</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1550000</v>
+        <v>240000000</v>
       </c>
       <c r="G98" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H98" s="8">
         <f>IF($E98*'설정'!$C$5*IF(('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)&lt;1,('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$6),('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E98*'설정'!$C$5*IF(('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)&lt;1,('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$6),('설정'!$C$22*IF($A98&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D98)^(-'설정'!$C$7)),0))</f>
@@ -10353,16 +10353,16 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>91900000</v>
+        <v>3770000000</v>
       </c>
       <c r="E99" t="n">
-        <v>90</v>
+        <v>136.1</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>1840000</v>
+        <v>314000000</v>
       </c>
       <c r="G99" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H99" s="8">
         <f>IF($E99*'설정'!$C$5*IF(('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)&lt;1,('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$6),('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E99*'설정'!$C$5*IF(('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)&lt;1,('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$6),('설정'!$C$22*IF($A99&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D99)^(-'설정'!$C$7)),0))</f>
@@ -10440,16 +10440,16 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" s="6" t="n">
-        <v>82300000</v>
+        <v>3520000000</v>
       </c>
       <c r="E100" t="n">
-        <v>72</v>
+        <v>109.4</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>1650000</v>
+        <v>294000000</v>
       </c>
       <c r="G100" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H100" s="8">
         <f>IF($E100*'설정'!$C$5*IF(('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)&lt;1,('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$6),('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E100*'설정'!$C$5*IF(('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)&lt;1,('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$6),('설정'!$C$22*IF($A100&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D100)^(-'설정'!$C$7)),0))</f>
@@ -10527,16 +10527,16 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" s="6" t="n">
-        <v>84800000</v>
+        <v>3750000000</v>
       </c>
       <c r="E101" t="n">
-        <v>72</v>
+        <v>109.9</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1700000</v>
+        <v>313000000</v>
       </c>
       <c r="G101" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H101" s="8">
         <f>IF($E101*'설정'!$C$5*IF(('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)&lt;1,('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$6),('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22),"실패",ROUND($E101*'설정'!$C$5*IF(('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)&lt;1,('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$6),('설정'!$C$22*IF($A101&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D101)^(-'설정'!$C$7)),0))</f>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>허들</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -10618,16 +10618,16 @@
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>122000000</v>
+        <v>4810000000</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>90</v>
+        <v>163.8</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>2440000</v>
+        <v>402000000</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H102" s="8">
         <f>IF($E102*'설정'!$C$5*IF(('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)&lt;1,('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$6),('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$7))&gt;('설정'!$C$4+'설정'!$F$22+'설정'!$G$22),"실패",ROUND($E102*'설정'!$C$5*IF(('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)&lt;1,('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$6),('설정'!$C$22*IF($A102&gt;=31,1+'설정'!$C$14*'설정'!$E$22,1)/$D102)^(-'설정'!$C$7)),0))</f>
@@ -10716,7 +10716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10798,22 +10798,22 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>31.21</v>
+        <v>63.37</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>32204.07185943312</v>
+        <v>154509.6862764244</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>13</v>
@@ -10824,37 +10824,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.32</v>
+        <v>0.68</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7</v>
+        <v>20.3</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>79.88</v>
+        <v>740.11</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>76397.02943566462</v>
+        <v>23726902.48375675</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -10862,37 +10862,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>255.69</v>
+        <v>1093.61</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>746259.9413222184</v>
+        <v>200568686.4364652</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -10900,37 +10900,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0.51</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>14.5</v>
+        <v>16.7</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>430.58</v>
+        <v>2255.11</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>5295268.189350614</v>
+        <v>2468962431.445557</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -10938,37 +10938,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.71</v>
+        <v>1.04</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>10.6</v>
+        <v>14.5</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>406.35</v>
+        <v>5695.610000000001</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>13612379.50113069</v>
+        <v>11705123916.60558</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -10976,37 +10976,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.89</v>
+        <v>1.28</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>461.86</v>
+        <v>8308.610000000001</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>26379454.91467971</v>
+        <v>18339493590.04018</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="L7" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -11014,37 +11014,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>255.3699999999999</v>
+        <v>11763.61</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>33436530.32822873</v>
+        <v>26723863263.47479</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -11052,37 +11052,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>745.8799999999999</v>
+        <v>33454.61</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>108336448.7079646</v>
+        <v>95677103007.47336</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -11090,37 +11090,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>10.3</v>
+        <v>31.8</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>1063.88</v>
+        <v>398797.61</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>227426263.8683756</v>
+        <v>1784787589042.467</v>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -11128,37 +11128,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>18.6</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>568.8799999999999</v>
+        <v>561463.61</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>249916079.0287865</v>
+        <v>2724418961693.069</v>
       </c>
       <c r="K11" t="n">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -11166,37 +11166,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.75</v>
+        <v>2.67</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="H12" t="n">
-        <v>17.2</v>
+        <v>11.9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>2075.38</v>
+        <v>614275.61</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>1295457628.58637</v>
+        <v>3330159882470.052</v>
       </c>
       <c r="K12" t="n">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -11204,37 +11204,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2.03</v>
+        <v>2.86</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
-        <v>10.1</v>
+        <v>21.4</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>2877.88</v>
+        <v>1620183.61</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>2207399206.542687</v>
+        <v>10696857693314.95</v>
       </c>
       <c r="K13" t="n">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -11242,37 +11242,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="H14" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>2418.38</v>
+        <v>2208385.61</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>3654238978.611913</v>
+        <v>16115460022896.04</v>
       </c>
       <c r="K14" t="n">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -11280,37 +11280,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.41</v>
+        <v>3.44</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>3863.38</v>
+        <v>5326468.609999999</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>8690862409.628456</v>
+        <v>58800465702585.71</v>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="L15" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -11318,37 +11318,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2.61</v>
+        <v>3.76</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="H16" t="n">
-        <v>11.6</v>
+        <v>14.8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>7373.38</v>
+        <v>8141271.609999999</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>16402485840.645</v>
+        <v>95766276221923.53</v>
       </c>
       <c r="K16" t="n">
-        <v>107</v>
+        <v>254</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -11356,37 +11356,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="H17" t="n">
-        <v>10.3</v>
+        <v>14.8</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>5192.38</v>
+        <v>11635771.61</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>18321529081.40352</v>
+        <v>141572086741261.3</v>
       </c>
       <c r="K17" t="n">
-        <v>114</v>
+        <v>276</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -11394,37 +11394,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.98</v>
+        <v>4.25</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H18" t="n">
-        <v>21.2</v>
+        <v>16.5</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>20762.38</v>
+        <v>17295061.61</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>53709495384.35252</v>
+        <v>254468050723429.6</v>
       </c>
       <c r="K18" t="n">
-        <v>124</v>
+        <v>299</v>
       </c>
       <c r="L18" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -11432,37 +11432,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3.33</v>
+        <v>4.52</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1</v>
+        <v>0.16</v>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="G19" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>10.1</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>27135.38</v>
+        <v>30497704.61</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>70497308183.71701</v>
+        <v>671518095751678</v>
       </c>
       <c r="K19" t="n">
-        <v>141</v>
+        <v>328</v>
       </c>
       <c r="L19" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -11470,37 +11470,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.5</v>
+        <v>4.82</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="G20" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H20" t="n">
-        <v>18.6</v>
+        <v>12.2</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>38239.38</v>
+        <v>25780234.61</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>138746469952.0185</v>
+        <v>522243587372936.2</v>
       </c>
       <c r="K20" t="n">
-        <v>161</v>
+        <v>337</v>
       </c>
       <c r="L20" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -11508,37 +11508,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.81</v>
+        <v>5.02</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="H21" t="n">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>65710.38</v>
+        <v>47143687.61</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>217937871910.4391</v>
+        <v>1027398704773278</v>
       </c>
       <c r="K21" t="n">
-        <v>179</v>
+        <v>353</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
@@ -11546,37 +11546,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>4.08</v>
+        <v>5.27</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H22" t="n">
-        <v>9.9</v>
+        <v>14.7</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>30067.38</v>
+        <v>81793687.61</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>171802521881.4778</v>
+        <v>1848553822173621</v>
       </c>
       <c r="K22" t="n">
-        <v>186</v>
+        <v>363</v>
       </c>
       <c r="L22" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
@@ -11584,37 +11584,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>4.25</v>
+        <v>5.51</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1</v>
+        <v>0.27</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H23" t="n">
-        <v>9.9</v>
+        <v>21.8</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>54317.38</v>
+        <v>158164035.61</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>274567171852.5165</v>
+        <v>5482388692252409</v>
       </c>
       <c r="K23" t="n">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L23" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
@@ -11622,34 +11622,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>4.41</v>
+        <v>5.87</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="G24" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="H24" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>55222.38</v>
+        <v>172608141.61</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>463414213532.0444</v>
+        <v>5828836494903282</v>
       </c>
       <c r="K24" t="n">
-        <v>203</v>
+        <v>413</v>
       </c>
       <c r="L24" t="n">
         <v>87</v>
@@ -11660,34 +11660,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>4.65</v>
+        <v>6.12</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F25" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="G25" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="H25" t="n">
-        <v>8.800000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>51117.38</v>
+        <v>277508141.61</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>368187445785.2077</v>
+        <v>9095284297554156</v>
       </c>
       <c r="K25" t="n">
-        <v>215</v>
+        <v>426</v>
       </c>
       <c r="L25" t="n">
         <v>87</v>
@@ -11698,37 +11698,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>4.79</v>
+        <v>6.38</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F26" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H26" t="n">
-        <v>18.1</v>
+        <v>26.5</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>233515.38</v>
+        <v>684980296.61</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>1167179711253.314</v>
+        <v>2.884928570571657e+16</v>
       </c>
       <c r="K26" t="n">
-        <v>228</v>
+        <v>460</v>
       </c>
       <c r="L26" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
@@ -11736,37 +11736,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>5.09</v>
+        <v>6.82</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F27" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H27" t="n">
-        <v>9.699999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>136258.38</v>
+        <v>952099786.61</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>1426983134588.229</v>
+        <v>3.761317600799454e+16</v>
       </c>
       <c r="K27" t="n">
-        <v>245</v>
+        <v>500</v>
       </c>
       <c r="L27" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
@@ -11774,339 +11774,35 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>5.26</v>
+        <v>7.17</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
-      </c>
-      <c r="G28" t="n">
-        <v>64</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>21.5</v>
+        <v>11.4</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>581135.38</v>
+        <v>1194454732.61</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>3893122900611.269</v>
+        <v>5.673045329482775e+16</v>
       </c>
       <c r="K28" t="n">
-        <v>282</v>
+        <v>544</v>
       </c>
       <c r="L28" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="C29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E29" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" t="n">
-        <v>63</v>
-      </c>
-      <c r="G29" t="n">
-        <v>64</v>
-      </c>
-      <c r="H29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>341934.38</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>4534718557895.381</v>
-      </c>
-      <c r="K29" t="n">
-        <v>295</v>
-      </c>
-      <c r="L29" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="C30" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E30" t="n">
-        <v>60</v>
-      </c>
-      <c r="F30" t="n">
-        <v>69</v>
-      </c>
-      <c r="G30" t="n">
-        <v>70</v>
-      </c>
-      <c r="H30" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>1309789.38</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>10375017327010.46</v>
-      </c>
-      <c r="K30" t="n">
-        <v>316</v>
-      </c>
-      <c r="L30" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="C31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>66</v>
-      </c>
-      <c r="F31" t="n">
-        <v>69</v>
-      </c>
-      <c r="G31" t="n">
-        <v>70</v>
-      </c>
-      <c r="H31" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>1539386.38</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>11640782706026.4</v>
-      </c>
-      <c r="K31" t="n">
-        <v>322</v>
-      </c>
-      <c r="L31" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="C32" t="n">
-        <v>13</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E32" t="n">
-        <v>66</v>
-      </c>
-      <c r="F32" t="n">
-        <v>76</v>
-      </c>
-      <c r="G32" t="n">
-        <v>77</v>
-      </c>
-      <c r="H32" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>2552452.38</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>26179907981329.03</v>
-      </c>
-      <c r="K32" t="n">
-        <v>374</v>
-      </c>
-      <c r="L32" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="C33" t="n">
-        <v>14</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E33" t="n">
-        <v>73</v>
-      </c>
-      <c r="F33" t="n">
-        <v>83</v>
-      </c>
-      <c r="G33" t="n">
-        <v>84</v>
-      </c>
-      <c r="H33" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>3940690.38</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>48960835695510.09</v>
-      </c>
-      <c r="K33" t="n">
-        <v>421</v>
-      </c>
-      <c r="L33" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="C34" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>80</v>
-      </c>
-      <c r="F34" t="n">
-        <v>91</v>
-      </c>
-      <c r="G34" t="n">
-        <v>92</v>
-      </c>
-      <c r="H34" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>6443846.38</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>90166159383421.55</v>
-      </c>
-      <c r="K34" t="n">
-        <v>458</v>
-      </c>
-      <c r="L34" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>15</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>88</v>
-      </c>
-      <c r="F35" t="n">
-        <v>91</v>
-      </c>
-      <c r="G35" t="n">
-        <v>92</v>
-      </c>
-      <c r="H35" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>6073155.38</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>76805396941473.47</v>
-      </c>
-      <c r="K35" t="n">
-        <v>471</v>
-      </c>
-      <c r="L35" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="C36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>88</v>
-      </c>
-      <c r="F36" t="n">
-        <v>100</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>10869011.38</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>150276757290166.8</v>
-      </c>
-      <c r="K36" t="n">
-        <v>552</v>
-      </c>
-      <c r="L36" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -12120,7 +11816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12208,13 +11904,13 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>31.21</v>
+        <v>34.41</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>32204.07185943312</v>
+        <v>47553.55404697053</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -12228,13 +11924,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -12246,13 +11942,13 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>79.88</v>
+        <v>97.78</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>76397.02943566462</v>
+        <v>157163.240323395</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
@@ -12266,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -12278,25 +11974,25 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7</v>
+        <v>12.7</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>128.55</v>
+        <v>605.64</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>76589.98701189613</v>
+        <v>5219875.423354832</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -12304,37 +12000,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>13.8</v>
+        <v>21.4</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>304.36</v>
+        <v>1612.935</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>771752.8988984498</v>
+        <v>195455975.0718634</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -12342,37 +12038,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>19.8</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>219.5</v>
+        <v>2342.435</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>663086.7267105276</v>
+        <v>2426289720.080955</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -12380,37 +12076,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.77</v>
+        <v>1.14</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H7" t="n">
-        <v>14.7</v>
+        <v>16.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>504.39</v>
+        <v>5666.934999999999</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>5369594.974738923</v>
+        <v>11306351205.24098</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L7" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -12418,37 +12114,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>10.9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>289.14</v>
+        <v>8467.934999999999</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>4691852.033682284</v>
+        <v>18324720878.67558</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -12456,37 +12152,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>552.525</v>
+        <v>30158.935</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>22072319.41833667</v>
+        <v>87277960622.67415</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -12494,37 +12190,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.43</v>
+        <v>0.95</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>9.300000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>269.035</v>
+        <v>88174.935</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>20329394.83188569</v>
+        <v>305888498028.7234</v>
       </c>
       <c r="K10" t="n">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -12532,37 +12228,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="H11" t="n">
-        <v>13.2</v>
+        <v>27.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>557.545</v>
+        <v>454632.935</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>47186083.57677385</v>
+        <v>2192555675898.541</v>
       </c>
       <c r="K11" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -12570,37 +12266,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1.79</v>
+        <v>2.61</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="H12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>706.545</v>
+        <v>499717.935</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>101658963.4210624</v>
+        <v>2448560921013.326</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -12608,37 +12304,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>1085.545</v>
+        <v>474029.935</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>181531843.2653509</v>
+        <v>2565421468141.678</v>
       </c>
       <c r="K13" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -12646,37 +12342,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H14" t="n">
-        <v>9.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>561.5450000000001</v>
+        <v>555314.9350000001</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>193021658.4257619</v>
+        <v>3016830677949.208</v>
       </c>
       <c r="K14" t="n">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -12684,37 +12380,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.28</v>
+        <v>3.17</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>652.5450000000001</v>
+        <v>610723.9350000001</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>158911473.5861729</v>
+        <v>2809500929779.638</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="L15" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -12722,37 +12418,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2.43</v>
+        <v>3.34</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>0.95</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>2364.045</v>
+        <v>2070360.935</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>1285053023.143756</v>
+        <v>14694528212494.22</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -12760,37 +12456,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.24</v>
+        <v>0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H17" t="n">
-        <v>10.2</v>
+        <v>21</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1302.545</v>
+        <v>4108861.935</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>1752994601.100073</v>
+        <v>40769283415281.64</v>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -12798,37 +12494,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H18" t="n">
-        <v>9.300000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>1308.045</v>
+        <v>5587625.935000001</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>1233936179.05639</v>
+        <v>57534843457717.19</v>
       </c>
       <c r="K18" t="n">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L18" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -12836,37 +12532,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3.07</v>
+        <v>4.22</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.89</v>
+        <v>0.49</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>13.2</v>
+        <v>11.7</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>2887.545</v>
+        <v>3526290.935000001</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>3063775951.125617</v>
+        <v>51340653977055</v>
       </c>
       <c r="K19" t="n">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -12874,37 +12570,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.29</v>
+        <v>4.42</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="H20" t="n">
-        <v>8.6</v>
+        <v>18.7</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>3579.545</v>
+        <v>12896126.935</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>5254553401.474928</v>
+        <v>172914844194747.3</v>
       </c>
       <c r="K20" t="n">
-        <v>109</v>
+        <v>301</v>
       </c>
       <c r="L20" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -12912,37 +12608,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.44</v>
+        <v>4.73</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="H21" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>4979.545</v>
+        <v>13395658.935</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>8345330851.82424</v>
+        <v>182939915829811.1</v>
       </c>
       <c r="K21" t="n">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="L21" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
@@ -12950,37 +12646,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3.58</v>
+        <v>4.89</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="G22" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H22" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>3707.545</v>
+        <v>10929658.935</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>13696954282.84078</v>
+        <v>329964429940049.5</v>
       </c>
       <c r="K22" t="n">
-        <v>118</v>
+        <v>327</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
@@ -12988,37 +12684,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3.79</v>
+        <v>5.09</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="G23" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="H23" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>5108.545</v>
+        <v>11307518.935</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>14015997523.5993</v>
+        <v>276988944050287.9</v>
       </c>
       <c r="K23" t="n">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c r="L23" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
@@ -13026,37 +12722,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3.97</v>
+        <v>5.27</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="H24" t="n">
-        <v>9.199999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>5368.545</v>
+        <v>39512873.935</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>11581675743.29689</v>
+        <v>751367060173399.2</v>
       </c>
       <c r="K24" t="n">
-        <v>137</v>
+        <v>357</v>
       </c>
       <c r="L24" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
@@ -13064,37 +12760,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>4.13</v>
+        <v>5.59</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>22585.545</v>
+        <v>30940041.935</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>52339642046.24589</v>
+        <v>541264480699794.4</v>
       </c>
       <c r="K25" t="n">
-        <v>148</v>
+        <v>366</v>
       </c>
       <c r="L25" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -13102,37 +12798,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>4.46</v>
+        <v>5.75</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="H26" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>11563.545</v>
+        <v>44090041.935</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>67507454845.61037</v>
+        <v>851161901226189.6</v>
       </c>
       <c r="K26" t="n">
-        <v>161</v>
+        <v>382</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
@@ -13140,37 +12836,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>4.64</v>
+        <v>5.92</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G27" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="H27" t="n">
-        <v>20.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>38041.545</v>
+        <v>57240041.935</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>126456616613.9118</v>
+        <v>1161059321752585</v>
       </c>
       <c r="K27" t="n">
-        <v>191</v>
+        <v>386</v>
       </c>
       <c r="L27" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
@@ -13178,37 +12874,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>4.98</v>
+        <v>6.08</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G28" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="H28" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>18148.545</v>
+        <v>70390041.935</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>137095354773.7277</v>
+        <v>1470956742278980</v>
       </c>
       <c r="K28" t="n">
-        <v>196</v>
+        <v>403</v>
       </c>
       <c r="L28" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
@@ -13216,37 +12912,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>5.15</v>
+        <v>6.24</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.78</v>
+        <v>0.14</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H29" t="n">
-        <v>19.3</v>
+        <v>11.5</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>49161.545</v>
+        <v>34880649.935</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>224239075045.3708</v>
+        <v>2038111859679322</v>
       </c>
       <c r="K29" t="n">
-        <v>212</v>
+        <v>409</v>
       </c>
       <c r="L29" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
@@ -13254,34 +12950,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>5.47</v>
+        <v>6.43</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="E30" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="H30" t="n">
-        <v>11.5</v>
+        <v>20.4</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>63778.545</v>
+        <v>124851333.935</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>283603725016.4095</v>
+        <v>4051113547198172</v>
       </c>
       <c r="K30" t="n">
-        <v>216</v>
+        <v>434</v>
       </c>
       <c r="L30" t="n">
         <v>87</v>
@@ -13292,37 +12988,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>5.67</v>
+        <v>6.77</v>
       </c>
       <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>86</v>
+      </c>
+      <c r="F31" t="n">
+        <v>87</v>
+      </c>
+      <c r="G31" t="n">
+        <v>88</v>
+      </c>
+      <c r="H31" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E31" t="n">
-        <v>47</v>
-      </c>
-      <c r="F31" t="n">
-        <v>51</v>
-      </c>
-      <c r="G31" t="n">
-        <v>52</v>
-      </c>
-      <c r="H31" t="n">
-        <v>15.1</v>
-      </c>
       <c r="I31" s="11" t="n">
-        <v>55459.545</v>
+        <v>95154495.935</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>416450766695.9373</v>
+        <v>3027326337935164</v>
       </c>
       <c r="K31" t="n">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="L31" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
@@ -13330,37 +13026,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>5.92</v>
+        <v>6.94</v>
       </c>
       <c r="C32" t="n">
+        <v>14</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>86</v>
+      </c>
+      <c r="F32" t="n">
+        <v>87</v>
+      </c>
+      <c r="G32" t="n">
+        <v>88</v>
+      </c>
+      <c r="H32" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E32" t="n">
-        <v>48</v>
-      </c>
-      <c r="F32" t="n">
-        <v>51</v>
-      </c>
-      <c r="G32" t="n">
-        <v>52</v>
-      </c>
-      <c r="H32" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="I32" s="11" t="n">
-        <v>49700.545</v>
+        <v>135354495.935</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>311223998949.1006</v>
+        <v>4275539128672156</v>
       </c>
       <c r="K32" t="n">
-        <v>233</v>
+        <v>442</v>
       </c>
       <c r="L32" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33">
@@ -13368,37 +13064,37 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>6.08</v>
+        <v>7.11</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F33" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="H33" t="n">
-        <v>21.1</v>
+        <v>10</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>231012.545</v>
+        <v>175554495.935</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>1103216264417.207</v>
+        <v>5523751919409148</v>
       </c>
       <c r="K33" t="n">
-        <v>257</v>
+        <v>450</v>
       </c>
       <c r="L33" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
@@ -13406,37 +13102,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>6.43</v>
+        <v>7.27</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F34" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="G34" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="H34" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>139330.545</v>
+        <v>215754495.935</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>1388019687752.122</v>
+        <v>6771964710146140</v>
       </c>
       <c r="K34" t="n">
-        <v>269</v>
+        <v>455</v>
       </c>
       <c r="L34" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
@@ -13444,37 +13140,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>6.62</v>
+        <v>7.44</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E35" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F35" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G35" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H35" t="n">
-        <v>22.3</v>
+        <v>11.6</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>474379.545</v>
+        <v>105846815.935</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>2983769049179.907</v>
+        <v>8988412512797013</v>
       </c>
       <c r="K35" t="n">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="L35" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
@@ -13482,37 +13178,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>6.99</v>
+        <v>7.63</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="E36" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F36" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="G36" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="H36" t="n">
-        <v>15.1</v>
+        <v>20.8</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>381367.545</v>
+        <v>362702325.935</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>4776793468529.646</v>
+        <v>1.6251788506488e+16</v>
       </c>
       <c r="K36" t="n">
-        <v>312</v>
+        <v>504</v>
       </c>
       <c r="L36" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
@@ -13520,37 +13216,37 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7.24</v>
+        <v>7.98</v>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.59</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="G37" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="H37" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>350530.545</v>
+        <v>266746140.935</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>3555389125813.759</v>
+        <v>1.193156550674638e+16</v>
       </c>
       <c r="K37" t="n">
-        <v>318</v>
+        <v>504</v>
       </c>
       <c r="L37" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
@@ -13558,37 +13254,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>7.41</v>
+        <v>8.15</v>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F38" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H38" t="n">
-        <v>23.2</v>
+        <v>10</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1336419.545</v>
+        <v>385246140.935</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>9635687894928.84</v>
+        <v>1.655134250700476e+16</v>
       </c>
       <c r="K38" t="n">
-        <v>353</v>
+        <v>525</v>
       </c>
       <c r="L38" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39">
@@ -13596,37 +13292,37 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7.8</v>
+        <v>8.31</v>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F39" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>668358.5449999999</v>
+        <v>503746140.935</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>12471453273944.77</v>
+        <v>2.117111950726314e+16</v>
       </c>
       <c r="K39" t="n">
-        <v>372</v>
+        <v>534</v>
       </c>
       <c r="L39" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40">
@@ -13634,37 +13330,37 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>8.48</v>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F40" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G40" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="H40" t="n">
-        <v>23.9</v>
+        <v>10</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>2559409.545</v>
+        <v>622246140.9349999</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>24770578549247.41</v>
+        <v>2.579089650752152e+16</v>
       </c>
       <c r="K40" t="n">
-        <v>406</v>
+        <v>543</v>
       </c>
       <c r="L40" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41">
@@ -13672,149 +13368,35 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>8.4</v>
+        <v>8.65</v>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="E41" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F41" t="n">
-        <v>76</v>
-      </c>
-      <c r="G41" t="n">
-        <v>77</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>10.8</v>
+        <v>20.7</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>1159334.545</v>
+        <v>1186390844.935</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>23899112958616.86</v>
+        <v>6.345817379435472e+16</v>
       </c>
       <c r="K41" t="n">
-        <v>422</v>
+        <v>568</v>
       </c>
       <c r="L41" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="C42" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E42" t="n">
-        <v>73</v>
-      </c>
-      <c r="F42" t="n">
-        <v>83</v>
-      </c>
-      <c r="G42" t="n">
-        <v>84</v>
-      </c>
-      <c r="H42" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>4030971.545</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>44170040672797.92</v>
-      </c>
-      <c r="K42" t="n">
-        <v>462</v>
-      </c>
-      <c r="L42" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="C43" t="n">
-        <v>15</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E43" t="n">
-        <v>80</v>
-      </c>
-      <c r="F43" t="n">
-        <v>91</v>
-      </c>
-      <c r="G43" t="n">
-        <v>92</v>
-      </c>
-      <c r="H43" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>6471117.545</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>82505364360709.38</v>
-      </c>
-      <c r="K43" t="n">
-        <v>490</v>
-      </c>
-      <c r="L43" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="C44" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E44" t="n">
-        <v>88</v>
-      </c>
-      <c r="F44" t="n">
-        <v>100</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>10340306.545</v>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>143926724709402.7</v>
-      </c>
-      <c r="K44" t="n">
-        <v>564</v>
-      </c>
-      <c r="L44" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
